--- a/Hamster Sand - 17.08.2026 (1).xlsx
+++ b/Hamster Sand - 17.08.2026 (1).xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F476"/>
+  <dimension ref="A1:F470"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.38" customWidth="1" min="1" max="1"/>
@@ -2960,14 +2960,14 @@
         </is>
       </c>
       <c r="D156" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E156" s="5">
-        <f>SUM(D156:D167)</f>
+        <f>SUM(D156:D165)</f>
         <v/>
       </c>
       <c r="F156" s="6">
-        <f>SUM(E156:E195)</f>
+        <f>SUM(E156:E192)</f>
         <v/>
       </c>
     </row>
@@ -2989,7 +2989,7 @@
     <row r="158">
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>quite enjoyed the sand</t>
+          <t>working very well</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
@@ -3004,7 +3004,7 @@
     <row r="159">
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>working very well</t>
+          <t>quite enjoyed the sand</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
@@ -3013,13 +3013,13 @@
         </is>
       </c>
       <c r="D159" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>The sand is great quality</t>
+          <t>finally found the right sand for my hamster after a month of searching</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
@@ -3028,13 +3028,13 @@
         </is>
       </c>
       <c r="D160" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>did the trick perfectly</t>
+          <t>Esta muy Buena calidad y precio</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
@@ -3049,7 +3049,7 @@
     <row r="162">
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>finally found the right sand for my hamster after a month of searching</t>
+          <t>Great sand at a great price for hamsters</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
@@ -3064,7 +3064,7 @@
     <row r="163">
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>Esta muy Buena calidad y precio</t>
+          <t>excellent quality</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
@@ -3079,7 +3079,7 @@
     <row r="164">
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>Great sand at a great price for hamsters</t>
+          <t>I love this sandbath for my hamsters</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
@@ -3094,7 +3094,7 @@
     <row r="165">
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>excellent quality</t>
+          <t>Sand comes as described!</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
@@ -3107,39 +3107,43 @@
       </c>
     </row>
     <row r="166">
-      <c r="B166" s="3" t="inlineStr">
-        <is>
-          <t>I love this sandbath for my hamsters</t>
-        </is>
-      </c>
-      <c r="C166" s="4" t="inlineStr">
-        <is>
-          <t>JFWOD</t>
-        </is>
-      </c>
-      <c r="D166" s="4" t="n">
-        <v>1</v>
+      <c r="B166" s="7" t="inlineStr">
+        <is>
+          <t>working very well</t>
+        </is>
+      </c>
+      <c r="C166" s="8" t="inlineStr">
+        <is>
+          <t>DR_DUDU</t>
+        </is>
+      </c>
+      <c r="D166" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E166" s="5">
+        <f>SUM(D166:D171)</f>
+        <v/>
       </c>
     </row>
     <row r="167">
-      <c r="B167" s="3" t="inlineStr">
-        <is>
-          <t>Sand comes as described!</t>
-        </is>
-      </c>
-      <c r="C167" s="4" t="inlineStr">
-        <is>
-          <t>JFWOD</t>
-        </is>
-      </c>
-      <c r="D167" s="4" t="n">
-        <v>1</v>
+      <c r="B167" s="7" t="inlineStr">
+        <is>
+          <t>This sand is great for hamsters</t>
+        </is>
+      </c>
+      <c r="C167" s="8" t="inlineStr">
+        <is>
+          <t>DR_DUDU</t>
+        </is>
+      </c>
+      <c r="D167" s="8" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="168">
       <c r="B168" s="7" t="inlineStr">
         <is>
-          <t>This sand is great for hamsters</t>
+          <t>good quality sand</t>
         </is>
       </c>
       <c r="C168" s="8" t="inlineStr">
@@ -3148,17 +3152,13 @@
         </is>
       </c>
       <c r="D168" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="E168" s="5">
-        <f>SUM(D168:D174)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
       <c r="B169" s="7" t="inlineStr">
         <is>
-          <t>working very well</t>
+          <t>Very good sand fr hammys they liked it</t>
         </is>
       </c>
       <c r="C169" s="8" t="inlineStr">
@@ -3167,13 +3167,13 @@
         </is>
       </c>
       <c r="D169" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170">
       <c r="B170" s="7" t="inlineStr">
         <is>
-          <t>good quality sand</t>
+          <t>she is naturally drawn to it</t>
         </is>
       </c>
       <c r="C170" s="8" t="inlineStr">
@@ -3188,7 +3188,7 @@
     <row r="171">
       <c r="B171" s="7" t="inlineStr">
         <is>
-          <t>Very good sand fr hammys they liked it</t>
+          <t>I love this sandbath for my hamsters</t>
         </is>
       </c>
       <c r="C171" s="8" t="inlineStr">
@@ -3201,54 +3201,58 @@
       </c>
     </row>
     <row r="172">
-      <c r="B172" s="7" t="inlineStr">
-        <is>
-          <t>does it well</t>
-        </is>
-      </c>
-      <c r="C172" s="8" t="inlineStr">
-        <is>
-          <t>DR_DUDU</t>
-        </is>
-      </c>
-      <c r="D172" s="8" t="n">
-        <v>1</v>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>This sand is great for hamsters</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="inlineStr">
+        <is>
+          <t>Hamiledyi</t>
+        </is>
+      </c>
+      <c r="D172" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E172" s="5">
+        <f>SUM(D172:D180)</f>
+        <v/>
       </c>
     </row>
     <row r="173">
-      <c r="B173" s="7" t="inlineStr">
-        <is>
-          <t>she is naturally drawn to it</t>
-        </is>
-      </c>
-      <c r="C173" s="8" t="inlineStr">
-        <is>
-          <t>DR_DUDU</t>
-        </is>
-      </c>
-      <c r="D173" s="8" t="n">
-        <v>1</v>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>good quality sand</t>
+        </is>
+      </c>
+      <c r="C173" s="4" t="inlineStr">
+        <is>
+          <t>Hamiledyi</t>
+        </is>
+      </c>
+      <c r="D173" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="174">
-      <c r="B174" s="7" t="inlineStr">
-        <is>
-          <t>I love this sandbath for my hamsters</t>
-        </is>
-      </c>
-      <c r="C174" s="8" t="inlineStr">
-        <is>
-          <t>DR_DUDU</t>
-        </is>
-      </c>
-      <c r="D174" s="8" t="n">
-        <v>1</v>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>working very well</t>
+        </is>
+      </c>
+      <c r="C174" s="4" t="inlineStr">
+        <is>
+          <t>Hamiledyi</t>
+        </is>
+      </c>
+      <c r="D174" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="175">
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>This sand is great for hamsters</t>
+          <t>the quality of the sand is just as good as the one I buy at the pet store</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
@@ -3257,17 +3261,13 @@
         </is>
       </c>
       <c r="D175" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E175" s="5">
-        <f>SUM(D175:D183)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="176">
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>good quality sand</t>
+          <t>this sand has been great for them all and safe</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
@@ -3276,13 +3276,13 @@
         </is>
       </c>
       <c r="D176" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>working very well</t>
+          <t>it's true sand not powder</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
@@ -3291,13 +3291,13 @@
         </is>
       </c>
       <c r="D177" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178">
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>the quality of the sand is just as good as the one I buy at the pet store</t>
+          <t>this is sand texture and appears very safe</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
@@ -3312,7 +3312,7 @@
     <row r="179">
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>this sand has been great for them all and safe</t>
+          <t>Great for dwarf hamsters</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
@@ -3327,7 +3327,7 @@
     <row r="180">
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>it's true sand not powder</t>
+          <t>The best sand I ever use</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
@@ -3340,103 +3340,107 @@
       </c>
     </row>
     <row r="181">
-      <c r="B181" s="3" t="inlineStr">
-        <is>
-          <t>this is sand texture and appears very safe</t>
-        </is>
-      </c>
-      <c r="C181" s="4" t="inlineStr">
-        <is>
-          <t>Hamiledyi</t>
-        </is>
-      </c>
-      <c r="D181" s="4" t="n">
-        <v>1</v>
+      <c r="B181" s="7" t="inlineStr">
+        <is>
+          <t>working very well</t>
+        </is>
+      </c>
+      <c r="C181" s="8" t="inlineStr">
+        <is>
+          <t>Sukh</t>
+        </is>
+      </c>
+      <c r="D181" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E181" s="5">
+        <f>SUM(D181:D183)</f>
+        <v/>
       </c>
     </row>
     <row r="182">
-      <c r="B182" s="3" t="inlineStr">
-        <is>
-          <t>Great for dwarf hamsters</t>
-        </is>
-      </c>
-      <c r="C182" s="4" t="inlineStr">
-        <is>
-          <t>Hamiledyi</t>
-        </is>
-      </c>
-      <c r="D182" s="4" t="n">
-        <v>1</v>
+      <c r="B182" s="7" t="inlineStr">
+        <is>
+          <t>good quality sand</t>
+        </is>
+      </c>
+      <c r="C182" s="8" t="inlineStr">
+        <is>
+          <t>Sukh</t>
+        </is>
+      </c>
+      <c r="D182" s="8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="183">
-      <c r="B183" s="3" t="inlineStr">
-        <is>
-          <t>The best sand I ever use</t>
-        </is>
-      </c>
-      <c r="C183" s="4" t="inlineStr">
-        <is>
-          <t>Hamiledyi</t>
-        </is>
-      </c>
-      <c r="D183" s="4" t="n">
+      <c r="B183" s="7" t="inlineStr">
+        <is>
+          <t>I change it regularly, and it's made a big difference</t>
+        </is>
+      </c>
+      <c r="C183" s="8" t="inlineStr">
+        <is>
+          <t>Sukh</t>
+        </is>
+      </c>
+      <c r="D183" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="184">
-      <c r="B184" s="7" t="inlineStr">
+      <c r="B184" s="3" t="inlineStr">
         <is>
           <t>working very well</t>
         </is>
       </c>
-      <c r="C184" s="8" t="inlineStr">
-        <is>
-          <t>Sukh</t>
-        </is>
-      </c>
-      <c r="D184" s="8" t="n">
-        <v>3</v>
+      <c r="C184" s="4" t="inlineStr">
+        <is>
+          <t>Fufuzoie</t>
+        </is>
+      </c>
+      <c r="D184" s="4" t="n">
+        <v>2</v>
       </c>
       <c r="E184" s="5">
-        <f>SUM(D184:D186)</f>
+        <f>SUM(D184:D188)</f>
         <v/>
       </c>
     </row>
     <row r="185">
-      <c r="B185" s="7" t="inlineStr">
+      <c r="B185" s="3" t="inlineStr">
         <is>
           <t>good quality sand</t>
         </is>
       </c>
-      <c r="C185" s="8" t="inlineStr">
-        <is>
-          <t>Sukh</t>
-        </is>
-      </c>
-      <c r="D185" s="8" t="n">
-        <v>2</v>
+      <c r="C185" s="4" t="inlineStr">
+        <is>
+          <t>Fufuzoie</t>
+        </is>
+      </c>
+      <c r="D185" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="186">
-      <c r="B186" s="7" t="inlineStr">
-        <is>
-          <t>I change it regularly, and it's made a big difference</t>
-        </is>
-      </c>
-      <c r="C186" s="8" t="inlineStr">
-        <is>
-          <t>Sukh</t>
-        </is>
-      </c>
-      <c r="D186" s="8" t="n">
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>The sand itself is good quality, odorless, minimal dust and smooth, pure granules</t>
+        </is>
+      </c>
+      <c r="C186" s="4" t="inlineStr">
+        <is>
+          <t>Fufuzoie</t>
+        </is>
+      </c>
+      <c r="D186" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="187">
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>working very well</t>
+          <t>haven't been any impurities in the sand</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
@@ -3445,150 +3449,154 @@
         </is>
       </c>
       <c r="D187" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E187" s="5">
-        <f>SUM(D187:D191)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="188">
       <c r="B188" s="3" t="inlineStr">
         <is>
+          <t>It really mimics a natural desert environment</t>
+        </is>
+      </c>
+      <c r="C188" s="4" t="inlineStr">
+        <is>
+          <t>Fufuzoie</t>
+        </is>
+      </c>
+      <c r="D188" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" s="7" t="inlineStr">
+        <is>
           <t>good quality sand</t>
         </is>
       </c>
-      <c r="C188" s="4" t="inlineStr">
-        <is>
-          <t>Fufuzoie</t>
-        </is>
-      </c>
-      <c r="D188" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="B189" s="3" t="inlineStr">
-        <is>
-          <t>The sand itself is good quality, odorless, minimal dust and smooth, pure granules</t>
-        </is>
-      </c>
-      <c r="C189" s="4" t="inlineStr">
-        <is>
-          <t>Fufuzoie</t>
-        </is>
-      </c>
-      <c r="D189" s="4" t="n">
-        <v>1</v>
+      <c r="C189" s="8" t="inlineStr">
+        <is>
+          <t>Meow&amp;Woof</t>
+        </is>
+      </c>
+      <c r="D189" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E189" s="5">
+        <f>SUM(D189:D190)</f>
+        <v/>
       </c>
     </row>
     <row r="190">
-      <c r="B190" s="3" t="inlineStr">
-        <is>
-          <t>haven't been any impurities in the sand</t>
-        </is>
-      </c>
-      <c r="C190" s="4" t="inlineStr">
-        <is>
-          <t>Fufuzoie</t>
-        </is>
-      </c>
-      <c r="D190" s="4" t="n">
+      <c r="B190" s="7" t="inlineStr">
+        <is>
+          <t>This sand is great for hamsters</t>
+        </is>
+      </c>
+      <c r="C190" s="8" t="inlineStr">
+        <is>
+          <t>Meow&amp;Woof</t>
+        </is>
+      </c>
+      <c r="D190" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="191">
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>It really mimics a natural desert environment</t>
+          <t>the sand will be safe for my hamsters</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Fufuzoie</t>
+          <t>BUCATSTATE</t>
         </is>
       </c>
       <c r="D191" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="E191" s="5">
+        <f>SUM(D191:D192)</f>
+        <v/>
+      </c>
     </row>
     <row r="192">
-      <c r="B192" s="7" t="inlineStr">
-        <is>
-          <t>good quality sand</t>
-        </is>
-      </c>
-      <c r="C192" s="8" t="inlineStr">
-        <is>
-          <t>Meow&amp;Woof</t>
-        </is>
-      </c>
-      <c r="D192" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E192" s="5">
-        <f>SUM(D192:D193)</f>
-        <v/>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>the quality of the sand is just as good as the one I buy at the pet store</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="inlineStr">
+        <is>
+          <t>BUCATSTATE</t>
+        </is>
+      </c>
+      <c r="D192" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="193">
-      <c r="B193" s="7" t="inlineStr">
-        <is>
-          <t>This sand is great for hamsters</t>
-        </is>
-      </c>
-      <c r="C193" s="8" t="inlineStr">
-        <is>
-          <t>Meow&amp;Woof</t>
-        </is>
-      </c>
-      <c r="D193" s="8" t="n">
-        <v>1</v>
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>Easy to Clean</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>easy to clean</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>DR_DUDU</t>
+        </is>
+      </c>
+      <c r="D193" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E193" s="5">
+        <f>SUM(D193:D201)</f>
+        <v/>
+      </c>
+      <c r="F193" s="6">
+        <f>SUM(E193:E226)</f>
+        <v/>
       </c>
     </row>
     <row r="194">
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>the sand will be safe for my hamsters</t>
+          <t>it helps keep the hamster clean</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>BUCATSTATE</t>
+          <t>DR_DUDU</t>
         </is>
       </c>
       <c r="D194" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E194" s="5">
-        <f>SUM(D194:D195)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="195">
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>the quality of the sand is just as good as the one I buy at the pet store</t>
+          <t>It's very clean</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>BUCATSTATE</t>
+          <t>DR_DUDU</t>
         </is>
       </c>
       <c r="D195" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="inlineStr">
-        <is>
-          <t>Easy to Clean</t>
-        </is>
-      </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>easy to clean</t>
+          <t>very easy to use</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
@@ -3597,21 +3605,13 @@
         </is>
       </c>
       <c r="D196" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E196" s="5">
-        <f>SUM(D196:D204)</f>
-        <v/>
-      </c>
-      <c r="F196" s="6">
-        <f>SUM(E196:E229)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="197">
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>it helps keep the hamster clean</t>
+          <t>is generally easy to remove with the sifter</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
@@ -3620,13 +3620,13 @@
         </is>
       </c>
       <c r="D197" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>It's very clean</t>
+          <t>Much easier to clean their enclosure which makes it safer for them</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
@@ -3635,13 +3635,13 @@
         </is>
       </c>
       <c r="D198" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>very easy to use</t>
+          <t>Doesn't stick on my babies</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="D199" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200">
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>is generally easy to remove with the sifter</t>
+          <t>it holds together so its easier to clean</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
@@ -3671,7 +3671,7 @@
     <row r="201">
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>Much easier to clean their enclosure which makes it safer for them</t>
+          <t>it's so easy to see when it needs to be cleaned</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
@@ -3684,54 +3684,58 @@
       </c>
     </row>
     <row r="202">
-      <c r="B202" s="3" t="inlineStr">
-        <is>
-          <t>Doesn't stick on my babies</t>
-        </is>
-      </c>
-      <c r="C202" s="4" t="inlineStr">
-        <is>
-          <t>DR_DUDU</t>
-        </is>
-      </c>
-      <c r="D202" s="4" t="n">
-        <v>1</v>
+      <c r="B202" s="7" t="inlineStr">
+        <is>
+          <t>It's very clean</t>
+        </is>
+      </c>
+      <c r="C202" s="8" t="inlineStr">
+        <is>
+          <t>JFWOD</t>
+        </is>
+      </c>
+      <c r="D202" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E202" s="5">
+        <f>SUM(D202:D207)</f>
+        <v/>
       </c>
     </row>
     <row r="203">
-      <c r="B203" s="3" t="inlineStr">
-        <is>
-          <t>it holds together so its easier to clean</t>
-        </is>
-      </c>
-      <c r="C203" s="4" t="inlineStr">
-        <is>
-          <t>DR_DUDU</t>
-        </is>
-      </c>
-      <c r="D203" s="4" t="n">
-        <v>1</v>
+      <c r="B203" s="7" t="inlineStr">
+        <is>
+          <t>easy to clean</t>
+        </is>
+      </c>
+      <c r="C203" s="8" t="inlineStr">
+        <is>
+          <t>JFWOD</t>
+        </is>
+      </c>
+      <c r="D203" s="8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="204">
-      <c r="B204" s="3" t="inlineStr">
-        <is>
-          <t>it's so easy to see when it needs to be cleaned</t>
-        </is>
-      </c>
-      <c r="C204" s="4" t="inlineStr">
-        <is>
-          <t>DR_DUDU</t>
-        </is>
-      </c>
-      <c r="D204" s="4" t="n">
-        <v>1</v>
+      <c r="B204" s="7" t="inlineStr">
+        <is>
+          <t>Bedding stays much cleaner and smells much better longer</t>
+        </is>
+      </c>
+      <c r="C204" s="8" t="inlineStr">
+        <is>
+          <t>JFWOD</t>
+        </is>
+      </c>
+      <c r="D204" s="8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="205">
       <c r="B205" s="7" t="inlineStr">
         <is>
-          <t>It's very clean</t>
+          <t>is generally easy to remove with the sifter</t>
         </is>
       </c>
       <c r="C205" s="8" t="inlineStr">
@@ -3740,17 +3744,13 @@
         </is>
       </c>
       <c r="D205" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="E205" s="5">
-        <f>SUM(D205:D210)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="206">
       <c r="B206" s="7" t="inlineStr">
         <is>
-          <t>easy to clean</t>
+          <t>Healthy for my hammies to clean themselves</t>
         </is>
       </c>
       <c r="C206" s="8" t="inlineStr">
@@ -3759,13 +3759,13 @@
         </is>
       </c>
       <c r="D206" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207">
       <c r="B207" s="7" t="inlineStr">
         <is>
-          <t>Bedding stays much cleaner and smells much better longer</t>
+          <t>this sandbox has resulted in my not having to clean his cage as often</t>
         </is>
       </c>
       <c r="C207" s="8" t="inlineStr">
@@ -3774,58 +3774,62 @@
         </is>
       </c>
       <c r="D207" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208">
-      <c r="B208" s="7" t="inlineStr">
-        <is>
-          <t>is generally easy to remove with the sifter</t>
-        </is>
-      </c>
-      <c r="C208" s="8" t="inlineStr">
-        <is>
-          <t>JFWOD</t>
-        </is>
-      </c>
-      <c r="D208" s="8" t="n">
-        <v>1</v>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>easy to clean</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="inlineStr">
+        <is>
+          <t>Hamiledyi</t>
+        </is>
+      </c>
+      <c r="D208" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E208" s="5">
+        <f>SUM(D208:D213)</f>
+        <v/>
       </c>
     </row>
     <row r="209">
-      <c r="B209" s="7" t="inlineStr">
-        <is>
-          <t>Healthy for my hammies to clean themselves</t>
-        </is>
-      </c>
-      <c r="C209" s="8" t="inlineStr">
-        <is>
-          <t>JFWOD</t>
-        </is>
-      </c>
-      <c r="D209" s="8" t="n">
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>it helps keep the hamster clean</t>
+        </is>
+      </c>
+      <c r="C209" s="4" t="inlineStr">
+        <is>
+          <t>Hamiledyi</t>
+        </is>
+      </c>
+      <c r="D209" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="210">
-      <c r="B210" s="7" t="inlineStr">
-        <is>
-          <t>this sandbox has resulted in my not having to clean his cage as often</t>
-        </is>
-      </c>
-      <c r="C210" s="8" t="inlineStr">
-        <is>
-          <t>JFWOD</t>
-        </is>
-      </c>
-      <c r="D210" s="8" t="n">
+      <c r="B210" s="3" t="inlineStr">
+        <is>
+          <t>Very pure, clean, and fine</t>
+        </is>
+      </c>
+      <c r="C210" s="4" t="inlineStr">
+        <is>
+          <t>Hamiledyi</t>
+        </is>
+      </c>
+      <c r="D210" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="211">
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>easy to clean</t>
+          <t>the dish wash still easy enough for him to use.</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
@@ -3834,17 +3838,13 @@
         </is>
       </c>
       <c r="D211" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="E211" s="5">
-        <f>SUM(D211:D216)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="212">
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>it helps keep the hamster clean</t>
+          <t>Makes it very easy to spot her poop pellets and clean</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
@@ -3859,7 +3859,7 @@
     <row r="213">
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>Very pure, clean, and fine</t>
+          <t>cleans up nicely too</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
@@ -3872,54 +3872,58 @@
       </c>
     </row>
     <row r="214">
-      <c r="B214" s="3" t="inlineStr">
-        <is>
-          <t>the dish wash still easy enough for him to use.</t>
-        </is>
-      </c>
-      <c r="C214" s="4" t="inlineStr">
-        <is>
-          <t>Hamiledyi</t>
-        </is>
-      </c>
-      <c r="D214" s="4" t="n">
-        <v>1</v>
+      <c r="B214" s="7" t="inlineStr">
+        <is>
+          <t>easy to clean</t>
+        </is>
+      </c>
+      <c r="C214" s="8" t="inlineStr">
+        <is>
+          <t>Fufuzoie</t>
+        </is>
+      </c>
+      <c r="D214" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E214" s="5">
+        <f>SUM(D214:D220)</f>
+        <v/>
       </c>
     </row>
     <row r="215">
-      <c r="B215" s="3" t="inlineStr">
-        <is>
-          <t>Makes it very easy to spot her poop pellets and clean</t>
-        </is>
-      </c>
-      <c r="C215" s="4" t="inlineStr">
-        <is>
-          <t>Hamiledyi</t>
-        </is>
-      </c>
-      <c r="D215" s="4" t="n">
+      <c r="B215" s="7" t="inlineStr">
+        <is>
+          <t>keeps small pets clean without being overly dusty</t>
+        </is>
+      </c>
+      <c r="C215" s="8" t="inlineStr">
+        <is>
+          <t>Fufuzoie</t>
+        </is>
+      </c>
+      <c r="D215" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="216">
-      <c r="B216" s="3" t="inlineStr">
-        <is>
-          <t>cleans up nicely too</t>
-        </is>
-      </c>
-      <c r="C216" s="4" t="inlineStr">
-        <is>
-          <t>Hamiledyi</t>
-        </is>
-      </c>
-      <c r="D216" s="4" t="n">
+      <c r="B216" s="7" t="inlineStr">
+        <is>
+          <t>sand stayed fairly clean and easy to scoop</t>
+        </is>
+      </c>
+      <c r="C216" s="8" t="inlineStr">
+        <is>
+          <t>Fufuzoie</t>
+        </is>
+      </c>
+      <c r="D216" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="217">
       <c r="B217" s="7" t="inlineStr">
         <is>
-          <t>easy to clean</t>
+          <t>improved his space</t>
         </is>
       </c>
       <c r="C217" s="8" t="inlineStr">
@@ -3928,17 +3932,13 @@
         </is>
       </c>
       <c r="D217" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E217" s="5">
-        <f>SUM(D217:D223)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="218">
       <c r="B218" s="7" t="inlineStr">
         <is>
-          <t>keeps small pets clean without being overly dusty</t>
+          <t>This sand is absorbent and clumps quickly when exposed to moisture, which makes cleaning the sand box or the whole habitat a bit easier and quicker</t>
         </is>
       </c>
       <c r="C218" s="8" t="inlineStr">
@@ -3953,7 +3953,7 @@
     <row r="219">
       <c r="B219" s="7" t="inlineStr">
         <is>
-          <t>sand stayed fairly clean and easy to scoop</t>
+          <t>incredibly easy to spot-clean soiled areas with a small sieve</t>
         </is>
       </c>
       <c r="C219" s="8" t="inlineStr">
@@ -3968,7 +3968,7 @@
     <row r="220">
       <c r="B220" s="7" t="inlineStr">
         <is>
-          <t>improved his space</t>
+          <t>It pours smoothly, doesn't clump, and stays clean longer than I expected for a natural sand product</t>
         </is>
       </c>
       <c r="C220" s="8" t="inlineStr">
@@ -3981,161 +3981,169 @@
       </c>
     </row>
     <row r="221">
-      <c r="B221" s="7" t="inlineStr">
-        <is>
-          <t>This sand is absorbent and clumps quickly when exposed to moisture, which makes cleaning the sand box or the whole habitat a bit easier and quicker</t>
-        </is>
-      </c>
-      <c r="C221" s="8" t="inlineStr">
-        <is>
-          <t>Fufuzoie</t>
-        </is>
-      </c>
-      <c r="D221" s="8" t="n">
-        <v>1</v>
+      <c r="B221" s="3" t="inlineStr">
+        <is>
+          <t>easy to clean</t>
+        </is>
+      </c>
+      <c r="C221" s="4" t="inlineStr">
+        <is>
+          <t>BUCATSTATE</t>
+        </is>
+      </c>
+      <c r="D221" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E221" s="5">
+        <f>SUM(D221:D223)</f>
+        <v/>
       </c>
     </row>
     <row r="222">
-      <c r="B222" s="7" t="inlineStr">
-        <is>
-          <t>incredibly easy to spot-clean soiled areas with a small sieve</t>
-        </is>
-      </c>
-      <c r="C222" s="8" t="inlineStr">
-        <is>
-          <t>Fufuzoie</t>
-        </is>
-      </c>
-      <c r="D222" s="8" t="n">
+      <c r="B222" s="3" t="inlineStr">
+        <is>
+          <t>Previously we had to sift the sand everyday to clean up the urine and now we can just scoop it up. Such a time saver.</t>
+        </is>
+      </c>
+      <c r="C222" s="4" t="inlineStr">
+        <is>
+          <t>BUCATSTATE</t>
+        </is>
+      </c>
+      <c r="D222" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="223">
-      <c r="B223" s="7" t="inlineStr">
-        <is>
-          <t>It pours smoothly, doesn't clump, and stays clean longer than I expected for a natural sand product</t>
-        </is>
-      </c>
-      <c r="C223" s="8" t="inlineStr">
-        <is>
-          <t>Fufuzoie</t>
-        </is>
-      </c>
-      <c r="D223" s="8" t="n">
+      <c r="B223" s="3" t="inlineStr">
+        <is>
+          <t>Such a time saver</t>
+        </is>
+      </c>
+      <c r="C223" s="4" t="inlineStr">
+        <is>
+          <t>BUCATSTATE</t>
+        </is>
+      </c>
+      <c r="D223" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="224">
-      <c r="B224" s="3" t="inlineStr">
-        <is>
-          <t>easy to clean</t>
-        </is>
-      </c>
-      <c r="C224" s="4" t="inlineStr">
-        <is>
-          <t>BUCATSTATE</t>
-        </is>
-      </c>
-      <c r="D224" s="4" t="n">
-        <v>4</v>
+      <c r="B224" s="7" t="inlineStr">
+        <is>
+          <t>my child was able to scoop it right out no mess</t>
+        </is>
+      </c>
+      <c r="C224" s="8" t="inlineStr">
+        <is>
+          <t>Sukh</t>
+        </is>
+      </c>
+      <c r="D224" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="E224" s="5">
-        <f>SUM(D224:D226)</f>
+        <f>SUM(D224:D225)</f>
         <v/>
       </c>
     </row>
     <row r="225">
-      <c r="B225" s="3" t="inlineStr">
-        <is>
-          <t>Previously we had to sift the sand everyday to clean up the urine and now we can just scoop it up. Such a time saver.</t>
-        </is>
-      </c>
-      <c r="C225" s="4" t="inlineStr">
-        <is>
-          <t>BUCATSTATE</t>
-        </is>
-      </c>
-      <c r="D225" s="4" t="n">
+      <c r="B225" s="7" t="inlineStr">
+        <is>
+          <t>It's perfect for keeping her cage more hygienic</t>
+        </is>
+      </c>
+      <c r="C225" s="8" t="inlineStr">
+        <is>
+          <t>Sukh</t>
+        </is>
+      </c>
+      <c r="D225" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="226">
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>Such a time saver</t>
+          <t>It's very clean</t>
         </is>
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>BUCATSTATE</t>
+          <t>Meow&amp;Woof</t>
         </is>
       </c>
       <c r="D226" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="E226" s="5">
+        <f>SUM(D226:D226)</f>
+        <v/>
+      </c>
     </row>
     <row r="227">
-      <c r="B227" s="7" t="inlineStr">
-        <is>
-          <t>my child was able to scoop it right out no mess</t>
-        </is>
-      </c>
-      <c r="C227" s="8" t="inlineStr">
-        <is>
-          <t>Sukh</t>
-        </is>
-      </c>
-      <c r="D227" s="8" t="n">
-        <v>1</v>
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>Good Value</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="inlineStr">
+        <is>
+          <t>good amount of sand for the price</t>
+        </is>
+      </c>
+      <c r="C227" s="4" t="inlineStr">
+        <is>
+          <t>JFWOD</t>
+        </is>
+      </c>
+      <c r="D227" s="4" t="n">
+        <v>6</v>
       </c>
       <c r="E227" s="5">
-        <f>SUM(D227:D228)</f>
+        <f>SUM(D227:D232)</f>
+        <v/>
+      </c>
+      <c r="F227" s="6">
+        <f>SUM(E227:E250)</f>
         <v/>
       </c>
     </row>
     <row r="228">
-      <c r="B228" s="7" t="inlineStr">
-        <is>
-          <t>It's perfect for keeping her cage more hygienic</t>
-        </is>
-      </c>
-      <c r="C228" s="8" t="inlineStr">
-        <is>
-          <t>Sukh</t>
-        </is>
-      </c>
-      <c r="D228" s="8" t="n">
-        <v>1</v>
+      <c r="B228" s="3" t="inlineStr">
+        <is>
+          <t>Great value</t>
+        </is>
+      </c>
+      <c r="C228" s="4" t="inlineStr">
+        <is>
+          <t>JFWOD</t>
+        </is>
+      </c>
+      <c r="D228" s="4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="229">
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>It's very clean</t>
+          <t>good value</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>Meow&amp;Woof</t>
+          <t>JFWOD</t>
         </is>
       </c>
       <c r="D229" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E229" s="5">
-        <f>SUM(D229:D229)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="inlineStr">
-        <is>
-          <t>Good Value</t>
-        </is>
-      </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>good amount of sand for the price</t>
+          <t>Esta muy Buena calidad y precio</t>
         </is>
       </c>
       <c r="C230" s="4" t="inlineStr">
@@ -4144,21 +4152,13 @@
         </is>
       </c>
       <c r="D230" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E230" s="5">
-        <f>SUM(D230:D236)</f>
-        <v/>
-      </c>
-      <c r="F230" s="6">
-        <f>SUM(E230:E256)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="231">
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>Great value</t>
+          <t>Great sand at a great price for hamsters</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
@@ -4167,334 +4167,355 @@
         </is>
       </c>
       <c r="D231" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232">
       <c r="B232" s="3" t="inlineStr">
         <is>
+          <t>worth it to make my little Penelope happy</t>
+        </is>
+      </c>
+      <c r="C232" s="4" t="inlineStr">
+        <is>
+          <t>JFWOD</t>
+        </is>
+      </c>
+      <c r="D232" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" s="7" t="inlineStr">
+        <is>
           <t>good value</t>
         </is>
       </c>
-      <c r="C232" s="4" t="inlineStr">
-        <is>
-          <t>JFWOD</t>
-        </is>
-      </c>
-      <c r="D232" s="4" t="n">
+      <c r="C233" s="8" t="inlineStr">
+        <is>
+          <t>BUCATSTATE</t>
+        </is>
+      </c>
+      <c r="D233" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E233" s="5">
+        <f>SUM(D233:D236)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="234">
+      <c r="B234" s="7" t="inlineStr">
+        <is>
+          <t>good amount of sand for the price</t>
+        </is>
+      </c>
+      <c r="C234" s="8" t="inlineStr">
+        <is>
+          <t>BUCATSTATE</t>
+        </is>
+      </c>
+      <c r="D234" s="8" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="233">
-      <c r="B233" s="3" t="inlineStr">
-        <is>
-          <t>The perfect amount for a good price</t>
-        </is>
-      </c>
-      <c r="C233" s="4" t="inlineStr">
-        <is>
-          <t>JFWOD</t>
-        </is>
-      </c>
-      <c r="D233" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="B234" s="3" t="inlineStr">
-        <is>
-          <t>Esta muy Buena calidad y precio</t>
-        </is>
-      </c>
-      <c r="C234" s="4" t="inlineStr">
-        <is>
-          <t>JFWOD</t>
-        </is>
-      </c>
-      <c r="D234" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
     <row r="235">
-      <c r="B235" s="3" t="inlineStr">
-        <is>
-          <t>Great sand at a great price for hamsters</t>
-        </is>
-      </c>
-      <c r="C235" s="4" t="inlineStr">
-        <is>
-          <t>JFWOD</t>
-        </is>
-      </c>
-      <c r="D235" s="4" t="n">
+      <c r="B235" s="7" t="inlineStr">
+        <is>
+          <t>Definitely a much better value than my old bathing sand from PetSmart</t>
+        </is>
+      </c>
+      <c r="C235" s="8" t="inlineStr">
+        <is>
+          <t>BUCATSTATE</t>
+        </is>
+      </c>
+      <c r="D235" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="236">
-      <c r="B236" s="3" t="inlineStr">
-        <is>
-          <t>worth it to make my little Penelope happy</t>
-        </is>
-      </c>
-      <c r="C236" s="4" t="inlineStr">
-        <is>
-          <t>JFWOD</t>
-        </is>
-      </c>
-      <c r="D236" s="4" t="n">
+      <c r="B236" s="7" t="inlineStr">
+        <is>
+          <t>I think it's a great value since there is less waste</t>
+        </is>
+      </c>
+      <c r="C236" s="8" t="inlineStr">
+        <is>
+          <t>BUCATSTATE</t>
+        </is>
+      </c>
+      <c r="D236" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="237">
-      <c r="B237" s="7" t="inlineStr">
+      <c r="B237" s="3" t="inlineStr">
+        <is>
+          <t>good amount of sand for the price</t>
+        </is>
+      </c>
+      <c r="C237" s="4" t="inlineStr">
+        <is>
+          <t>DR_DUDU</t>
+        </is>
+      </c>
+      <c r="D237" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E237" s="5">
+        <f>SUM(D237:D240)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="238">
+      <c r="B238" s="3" t="inlineStr">
+        <is>
+          <t>Great value</t>
+        </is>
+      </c>
+      <c r="C238" s="4" t="inlineStr">
+        <is>
+          <t>DR_DUDU</t>
+        </is>
+      </c>
+      <c r="D238" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="B239" s="3" t="inlineStr">
         <is>
           <t>good value</t>
         </is>
       </c>
-      <c r="C237" s="8" t="inlineStr">
-        <is>
-          <t>BUCATSTATE</t>
-        </is>
-      </c>
-      <c r="D237" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E237" s="5">
-        <f>SUM(D237:D241)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="238">
-      <c r="B238" s="7" t="inlineStr">
-        <is>
-          <t>Definitely a much better value than my old bathing sand from PetSmart</t>
-        </is>
-      </c>
-      <c r="C238" s="8" t="inlineStr">
-        <is>
-          <t>BUCATSTATE</t>
-        </is>
-      </c>
-      <c r="D238" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="B239" s="7" t="inlineStr">
-        <is>
-          <t>I think it's a great value since there is less waste</t>
-        </is>
-      </c>
-      <c r="C239" s="8" t="inlineStr">
-        <is>
-          <t>BUCATSTATE</t>
-        </is>
-      </c>
-      <c r="D239" s="8" t="n">
+      <c r="C239" s="4" t="inlineStr">
+        <is>
+          <t>DR_DUDU</t>
+        </is>
+      </c>
+      <c r="D239" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="240">
-      <c r="B240" s="7" t="inlineStr">
-        <is>
-          <t>The perfect amount for a good price</t>
-        </is>
-      </c>
-      <c r="C240" s="8" t="inlineStr">
-        <is>
-          <t>BUCATSTATE</t>
-        </is>
-      </c>
-      <c r="D240" s="8" t="n">
+      <c r="B240" s="3" t="inlineStr">
+        <is>
+          <t>is a decent price compared to pet store</t>
+        </is>
+      </c>
+      <c r="C240" s="4" t="inlineStr">
+        <is>
+          <t>DR_DUDU</t>
+        </is>
+      </c>
+      <c r="D240" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="241">
       <c r="B241" s="7" t="inlineStr">
         <is>
-          <t>This brings so much more sand for such a great price</t>
+          <t>good value</t>
         </is>
       </c>
       <c r="C241" s="8" t="inlineStr">
         <is>
-          <t>BUCATSTATE</t>
+          <t>Hamiledyi</t>
         </is>
       </c>
       <c r="D241" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="E241" s="5">
+        <f>SUM(D241:D245)</f>
+        <v/>
       </c>
     </row>
     <row r="242">
-      <c r="B242" s="3" t="inlineStr">
+      <c r="B242" s="7" t="inlineStr">
         <is>
           <t>Great value</t>
         </is>
       </c>
-      <c r="C242" s="4" t="inlineStr">
-        <is>
-          <t>DR_DUDU</t>
-        </is>
-      </c>
-      <c r="D242" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E242" s="5">
-        <f>SUM(D242:D246)</f>
-        <v/>
+      <c r="C242" s="8" t="inlineStr">
+        <is>
+          <t>Hamiledyi</t>
+        </is>
+      </c>
+      <c r="D242" s="8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="243">
-      <c r="B243" s="3" t="inlineStr">
+      <c r="B243" s="7" t="inlineStr">
         <is>
           <t>good amount of sand for the price</t>
         </is>
       </c>
-      <c r="C243" s="4" t="inlineStr">
-        <is>
-          <t>DR_DUDU</t>
-        </is>
-      </c>
-      <c r="D243" s="4" t="n">
-        <v>2</v>
+      <c r="C243" s="8" t="inlineStr">
+        <is>
+          <t>Hamiledyi</t>
+        </is>
+      </c>
+      <c r="D243" s="8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="244">
-      <c r="B244" s="3" t="inlineStr">
-        <is>
-          <t>good value</t>
-        </is>
-      </c>
-      <c r="C244" s="4" t="inlineStr">
-        <is>
-          <t>DR_DUDU</t>
-        </is>
-      </c>
-      <c r="D244" s="4" t="n">
+      <c r="B244" s="7" t="inlineStr">
+        <is>
+          <t>Good bathing sand for the price</t>
+        </is>
+      </c>
+      <c r="C244" s="8" t="inlineStr">
+        <is>
+          <t>Hamiledyi</t>
+        </is>
+      </c>
+      <c r="D244" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="245">
-      <c r="B245" s="3" t="inlineStr">
-        <is>
-          <t>Great price for quantity</t>
-        </is>
-      </c>
-      <c r="C245" s="4" t="inlineStr">
-        <is>
-          <t>DR_DUDU</t>
-        </is>
-      </c>
-      <c r="D245" s="4" t="n">
+      <c r="B245" s="7" t="inlineStr">
+        <is>
+          <t>a fantastic purchase, and most likely will be purchasing again!</t>
+        </is>
+      </c>
+      <c r="C245" s="8" t="inlineStr">
+        <is>
+          <t>Hamiledyi</t>
+        </is>
+      </c>
+      <c r="D245" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="246">
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>is a decent price compared to pet store</t>
+          <t>good value</t>
         </is>
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>DR_DUDU</t>
+          <t>Fufuzoie</t>
         </is>
       </c>
       <c r="D246" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="E246" s="5">
+        <f>SUM(D246:D249)</f>
+        <v/>
+      </c>
     </row>
     <row r="247">
-      <c r="B247" s="7" t="inlineStr">
-        <is>
-          <t>good value</t>
-        </is>
-      </c>
-      <c r="C247" s="8" t="inlineStr">
-        <is>
-          <t>Hamiledyi</t>
-        </is>
-      </c>
-      <c r="D247" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E247" s="5">
-        <f>SUM(D247:D251)</f>
-        <v/>
+      <c r="B247" s="3" t="inlineStr">
+        <is>
+          <t>makes things more affordable</t>
+        </is>
+      </c>
+      <c r="C247" s="4" t="inlineStr">
+        <is>
+          <t>Fufuzoie</t>
+        </is>
+      </c>
+      <c r="D247" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="248">
-      <c r="B248" s="7" t="inlineStr">
-        <is>
-          <t>Great value</t>
-        </is>
-      </c>
-      <c r="C248" s="8" t="inlineStr">
-        <is>
-          <t>Hamiledyi</t>
-        </is>
-      </c>
-      <c r="D248" s="8" t="n">
+      <c r="B248" s="3" t="inlineStr">
+        <is>
+          <t>it's priced appropriately based on how much use I get out of it</t>
+        </is>
+      </c>
+      <c r="C248" s="4" t="inlineStr">
+        <is>
+          <t>Fufuzoie</t>
+        </is>
+      </c>
+      <c r="D248" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="249">
-      <c r="B249" s="7" t="inlineStr">
-        <is>
-          <t>good amount of sand for the price</t>
-        </is>
-      </c>
-      <c r="C249" s="8" t="inlineStr">
-        <is>
-          <t>Hamiledyi</t>
-        </is>
-      </c>
-      <c r="D249" s="8" t="n">
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>This type of sand being a great addition to your pet hamster at a reasonable price</t>
+        </is>
+      </c>
+      <c r="C249" s="4" t="inlineStr">
+        <is>
+          <t>Fufuzoie</t>
+        </is>
+      </c>
+      <c r="D249" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="250">
       <c r="B250" s="7" t="inlineStr">
         <is>
-          <t>Good bathing sand for the price</t>
+          <t>The trial size is a good amount to test it out</t>
         </is>
       </c>
       <c r="C250" s="8" t="inlineStr">
         <is>
+          <t>Meow&amp;Woof</t>
+        </is>
+      </c>
+      <c r="D250" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E250" s="5">
+        <f>SUM(D250:D250)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>Sand Bathing</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="inlineStr">
+        <is>
+          <t>My hamster loves to bathe in it</t>
+        </is>
+      </c>
+      <c r="C251" s="4" t="inlineStr">
+        <is>
+          <t>JFWOD</t>
+        </is>
+      </c>
+      <c r="D251" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E251" s="5">
+        <f>SUM(D251:D251)</f>
+        <v/>
+      </c>
+      <c r="F251" s="6">
+        <f>SUM(E251:E266)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="252">
+      <c r="B252" s="7" t="inlineStr">
+        <is>
+          <t>My hamster loves to bathe in it</t>
+        </is>
+      </c>
+      <c r="C252" s="8" t="inlineStr">
+        <is>
           <t>Hamiledyi</t>
         </is>
       </c>
-      <c r="D250" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="B251" s="7" t="inlineStr">
-        <is>
-          <t>a fantastic purchase, and most likely will be purchasing again!</t>
-        </is>
-      </c>
-      <c r="C251" s="8" t="inlineStr">
-        <is>
-          <t>Hamiledyi</t>
-        </is>
-      </c>
-      <c r="D251" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="B252" s="3" t="inlineStr">
-        <is>
-          <t>good value</t>
-        </is>
-      </c>
-      <c r="C252" s="4" t="inlineStr">
-        <is>
-          <t>Fufuzoie</t>
-        </is>
-      </c>
-      <c r="D252" s="4" t="n">
-        <v>1</v>
+      <c r="D252" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="E252" s="5">
         <f>SUM(D252:D255)</f>
@@ -4502,140 +4523,127 @@
       </c>
     </row>
     <row r="253">
-      <c r="B253" s="3" t="inlineStr">
-        <is>
-          <t>makes things more affordable</t>
-        </is>
-      </c>
-      <c r="C253" s="4" t="inlineStr">
-        <is>
-          <t>Fufuzoie</t>
-        </is>
-      </c>
-      <c r="D253" s="4" t="n">
+      <c r="B253" s="7" t="inlineStr">
+        <is>
+          <t>I like this bath sand much more!</t>
+        </is>
+      </c>
+      <c r="C253" s="8" t="inlineStr">
+        <is>
+          <t>Hamiledyi</t>
+        </is>
+      </c>
+      <c r="D253" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="254">
-      <c r="B254" s="3" t="inlineStr">
-        <is>
-          <t>it's priced appropriately based on how much use I get out of it</t>
-        </is>
-      </c>
-      <c r="C254" s="4" t="inlineStr">
-        <is>
-          <t>Fufuzoie</t>
-        </is>
-      </c>
-      <c r="D254" s="4" t="n">
+      <c r="B254" s="7" t="inlineStr">
+        <is>
+          <t>Good bathing sand for the price</t>
+        </is>
+      </c>
+      <c r="C254" s="8" t="inlineStr">
+        <is>
+          <t>Hamiledyi</t>
+        </is>
+      </c>
+      <c r="D254" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="255">
-      <c r="B255" s="3" t="inlineStr">
-        <is>
-          <t>This type of sand being a great addition to your pet hamster at a reasonable price</t>
-        </is>
-      </c>
-      <c r="C255" s="4" t="inlineStr">
-        <is>
-          <t>Fufuzoie</t>
-        </is>
-      </c>
-      <c r="D255" s="4" t="n">
+      <c r="B255" s="7" t="inlineStr">
+        <is>
+          <t>perfect bath SAND for hamsters nice and fine</t>
+        </is>
+      </c>
+      <c r="C255" s="8" t="inlineStr">
+        <is>
+          <t>Hamiledyi</t>
+        </is>
+      </c>
+      <c r="D255" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="256">
-      <c r="B256" s="7" t="inlineStr">
-        <is>
-          <t>The trial size is a good amount to test it out</t>
-        </is>
-      </c>
-      <c r="C256" s="8" t="inlineStr">
-        <is>
-          <t>Meow&amp;Woof</t>
-        </is>
-      </c>
-      <c r="D256" s="8" t="n">
-        <v>1</v>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>My hamster loves to bathe in it</t>
+        </is>
+      </c>
+      <c r="C256" s="4" t="inlineStr">
+        <is>
+          <t>DR_DUDU</t>
+        </is>
+      </c>
+      <c r="D256" s="4" t="n">
+        <v>6</v>
       </c>
       <c r="E256" s="5">
-        <f>SUM(D256:D256)</f>
+        <f>SUM(D256:D258)</f>
         <v/>
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="inlineStr">
-        <is>
-          <t>Sand Bathing</t>
-        </is>
-      </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>My hamster loves to bathe in it</t>
+          <t>The sand is soft, fine, and perfect for my hamster's bathing needs</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>JFWOD</t>
+          <t>DR_DUDU</t>
         </is>
       </c>
       <c r="D257" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="E257" s="5">
-        <f>SUM(D257:D257)</f>
-        <v/>
-      </c>
-      <c r="F257" s="6">
-        <f>SUM(E257:E272)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="258">
-      <c r="B258" s="7" t="inlineStr">
-        <is>
-          <t>My hamster loves to bathe in it</t>
-        </is>
-      </c>
-      <c r="C258" s="8" t="inlineStr">
-        <is>
-          <t>Hamiledyi</t>
-        </is>
-      </c>
-      <c r="D258" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="E258" s="5">
-        <f>SUM(D258:D261)</f>
-        <v/>
+      <c r="B258" s="3" t="inlineStr">
+        <is>
+          <t>dust bath sand for my hamsters and they use it daily</t>
+        </is>
+      </c>
+      <c r="C258" s="4" t="inlineStr">
+        <is>
+          <t>DR_DUDU</t>
+        </is>
+      </c>
+      <c r="D258" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="259">
       <c r="B259" s="7" t="inlineStr">
         <is>
-          <t>I like this bath sand much more!</t>
+          <t>My hamster loves to bathe in it</t>
         </is>
       </c>
       <c r="C259" s="8" t="inlineStr">
         <is>
-          <t>Hamiledyi</t>
+          <t>BUCATSTATE</t>
         </is>
       </c>
       <c r="D259" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="E259" s="5">
+        <f>SUM(D259:D262)</f>
+        <v/>
       </c>
     </row>
     <row r="260">
       <c r="B260" s="7" t="inlineStr">
         <is>
-          <t>Good bathing sand for the price</t>
+          <t>I like this bath sand much more!</t>
         </is>
       </c>
       <c r="C260" s="8" t="inlineStr">
         <is>
-          <t>Hamiledyi</t>
+          <t>BUCATSTATE</t>
         </is>
       </c>
       <c r="D260" s="8" t="n">
@@ -4645,12 +4653,12 @@
     <row r="261">
       <c r="B261" s="7" t="inlineStr">
         <is>
-          <t>perfect bath SAND for hamsters nice and fine</t>
+          <t>My hamster rolls around in it and used it almost like a litter box</t>
         </is>
       </c>
       <c r="C261" s="8" t="inlineStr">
         <is>
-          <t>Hamiledyi</t>
+          <t>BUCATSTATE</t>
         </is>
       </c>
       <c r="D261" s="8" t="n">
@@ -4658,48 +4666,48 @@
       </c>
     </row>
     <row r="262">
-      <c r="B262" s="3" t="inlineStr">
-        <is>
-          <t>My hamster loves to bathe in it</t>
-        </is>
-      </c>
-      <c r="C262" s="4" t="inlineStr">
-        <is>
-          <t>DR_DUDU</t>
-        </is>
-      </c>
-      <c r="D262" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="E262" s="5">
-        <f>SUM(D262:D264)</f>
-        <v/>
+      <c r="B262" s="7" t="inlineStr">
+        <is>
+          <t>this dust is perfect for a bath dust</t>
+        </is>
+      </c>
+      <c r="C262" s="8" t="inlineStr">
+        <is>
+          <t>BUCATSTATE</t>
+        </is>
+      </c>
+      <c r="D262" s="8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="263">
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>The sand is soft, fine, and perfect for my hamster's bathing needs</t>
+          <t>My hamster loves to bathe in it</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>DR_DUDU</t>
+          <t>Fufuzoie</t>
         </is>
       </c>
       <c r="D263" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="E263" s="5">
+        <f>SUM(D263:D264)</f>
+        <v/>
       </c>
     </row>
     <row r="264">
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>dust bath sand for my hamsters and they use it daily</t>
+          <t>Good, clean, sand for hamster bath</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr">
         <is>
-          <t>DR_DUDU</t>
+          <t>Fufuzoie</t>
         </is>
       </c>
       <c r="D264" s="4" t="n">
@@ -4714,26 +4722,26 @@
       </c>
       <c r="C265" s="8" t="inlineStr">
         <is>
-          <t>BUCATSTATE</t>
+          <t>Sukh</t>
         </is>
       </c>
       <c r="D265" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E265" s="5">
-        <f>SUM(D265:D268)</f>
+        <f>SUM(D265:D266)</f>
         <v/>
       </c>
     </row>
     <row r="266">
       <c r="B266" s="7" t="inlineStr">
         <is>
-          <t>I like this bath sand much more!</t>
+          <t>She has a lil bath house and goes in and out to clean up as she pleases</t>
         </is>
       </c>
       <c r="C266" s="8" t="inlineStr">
         <is>
-          <t>BUCATSTATE</t>
+          <t>Sukh</t>
         </is>
       </c>
       <c r="D266" s="8" t="n">
@@ -4741,63 +4749,72 @@
       </c>
     </row>
     <row r="267">
-      <c r="B267" s="7" t="inlineStr">
-        <is>
-          <t>My hamster rolls around in it and used it almost like a litter box</t>
-        </is>
-      </c>
-      <c r="C267" s="8" t="inlineStr">
-        <is>
-          <t>BUCATSTATE</t>
-        </is>
-      </c>
-      <c r="D267" s="8" t="n">
-        <v>1</v>
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>Nice Color</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
+          <t>pure white</t>
+        </is>
+      </c>
+      <c r="C267" s="4" t="inlineStr">
+        <is>
+          <t>DR_DUDU</t>
+        </is>
+      </c>
+      <c r="D267" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E267" s="5">
+        <f>SUM(D267:D272)</f>
+        <v/>
+      </c>
+      <c r="F267" s="6">
+        <f>SUM(E267:E286)</f>
+        <v/>
       </c>
     </row>
     <row r="268">
-      <c r="B268" s="7" t="inlineStr">
-        <is>
-          <t>this dust is perfect for a bath dust</t>
-        </is>
-      </c>
-      <c r="C268" s="8" t="inlineStr">
-        <is>
-          <t>BUCATSTATE</t>
-        </is>
-      </c>
-      <c r="D268" s="8" t="n">
-        <v>1</v>
+      <c r="B268" s="3" t="inlineStr">
+        <is>
+          <t>It is white sand very, very fine</t>
+        </is>
+      </c>
+      <c r="C268" s="4" t="inlineStr">
+        <is>
+          <t>DR_DUDU</t>
+        </is>
+      </c>
+      <c r="D268" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="269">
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>My hamster loves to bathe in it</t>
+          <t>Very beautiful and fine sands</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>Fufuzoie</t>
+          <t>DR_DUDU</t>
         </is>
       </c>
       <c r="D269" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="E269" s="5">
-        <f>SUM(D269:D270)</f>
-        <v/>
       </c>
     </row>
     <row r="270">
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>Good, clean, sand for hamster bath</t>
+          <t>adds a little bit of color into his cage</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr">
         <is>
-          <t>Fufuzoie</t>
+          <t>DR_DUDU</t>
         </is>
       </c>
       <c r="D270" s="4" t="n">
@@ -4805,136 +4822,127 @@
       </c>
     </row>
     <row r="271">
-      <c r="B271" s="7" t="inlineStr">
-        <is>
-          <t>My hamster loves to bathe in it</t>
-        </is>
-      </c>
-      <c r="C271" s="8" t="inlineStr">
-        <is>
-          <t>Sukh</t>
-        </is>
-      </c>
-      <c r="D271" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E271" s="5">
-        <f>SUM(D271:D272)</f>
-        <v/>
+      <c r="B271" s="3" t="inlineStr">
+        <is>
+          <t>I like that it looks more natural</t>
+        </is>
+      </c>
+      <c r="C271" s="4" t="inlineStr">
+        <is>
+          <t>DR_DUDU</t>
+        </is>
+      </c>
+      <c r="D271" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="272">
-      <c r="B272" s="7" t="inlineStr">
-        <is>
-          <t>She has a lil bath house and goes in and out to clean up as she pleases</t>
-        </is>
-      </c>
-      <c r="C272" s="8" t="inlineStr">
-        <is>
-          <t>Sukh</t>
-        </is>
-      </c>
-      <c r="D272" s="8" t="n">
+      <c r="B272" s="3" t="inlineStr">
+        <is>
+          <t>It's white, clean, dense sand</t>
+        </is>
+      </c>
+      <c r="C272" s="4" t="inlineStr">
+        <is>
+          <t>DR_DUDU</t>
+        </is>
+      </c>
+      <c r="D272" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="2" t="inlineStr">
-        <is>
-          <t>Nice Color</t>
-        </is>
-      </c>
-      <c r="B273" s="3" t="inlineStr">
+      <c r="B273" s="7" t="inlineStr">
         <is>
           <t>pure white</t>
         </is>
       </c>
-      <c r="C273" s="4" t="inlineStr">
-        <is>
-          <t>DR_DUDU</t>
-        </is>
-      </c>
-      <c r="D273" s="4" t="n">
+      <c r="C273" s="8" t="inlineStr">
+        <is>
+          <t>JFWOD</t>
+        </is>
+      </c>
+      <c r="D273" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E273" s="5">
-        <f>SUM(D273:D278)</f>
-        <v/>
-      </c>
-      <c r="F273" s="6">
-        <f>SUM(E273:E292)</f>
+        <f>SUM(D273:D276)</f>
         <v/>
       </c>
     </row>
     <row r="274">
-      <c r="B274" s="3" t="inlineStr">
-        <is>
-          <t>It is white sand very, very fine</t>
-        </is>
-      </c>
-      <c r="C274" s="4" t="inlineStr">
-        <is>
-          <t>DR_DUDU</t>
-        </is>
-      </c>
-      <c r="D274" s="4" t="n">
-        <v>2</v>
+      <c r="B274" s="7" t="inlineStr">
+        <is>
+          <t>Clean, and pretty sand</t>
+        </is>
+      </c>
+      <c r="C274" s="8" t="inlineStr">
+        <is>
+          <t>JFWOD</t>
+        </is>
+      </c>
+      <c r="D274" s="8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="275">
-      <c r="B275" s="3" t="inlineStr">
-        <is>
-          <t>Very beautiful and fine sands</t>
-        </is>
-      </c>
-      <c r="C275" s="4" t="inlineStr">
-        <is>
-          <t>DR_DUDU</t>
-        </is>
-      </c>
-      <c r="D275" s="4" t="n">
+      <c r="B275" s="7" t="inlineStr">
+        <is>
+          <t>I like that it looks more natural</t>
+        </is>
+      </c>
+      <c r="C275" s="8" t="inlineStr">
+        <is>
+          <t>JFWOD</t>
+        </is>
+      </c>
+      <c r="D275" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="276">
-      <c r="B276" s="3" t="inlineStr">
-        <is>
-          <t>adds a little bit of color into his cage</t>
-        </is>
-      </c>
-      <c r="C276" s="4" t="inlineStr">
-        <is>
-          <t>DR_DUDU</t>
-        </is>
-      </c>
-      <c r="D276" s="4" t="n">
+      <c r="B276" s="7" t="inlineStr">
+        <is>
+          <t>It's white, clean, dense sand</t>
+        </is>
+      </c>
+      <c r="C276" s="8" t="inlineStr">
+        <is>
+          <t>JFWOD</t>
+        </is>
+      </c>
+      <c r="D276" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="277">
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>I like that it looks more natural</t>
+          <t>color blends well with the rest of his enclosure</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>DR_DUDU</t>
+          <t>Fufuzoie</t>
         </is>
       </c>
       <c r="D277" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="E277" s="5">
+        <f>SUM(D277:D281)</f>
+        <v/>
       </c>
     </row>
     <row r="278">
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>It's white, clean, dense sand</t>
+          <t>how bright white it is because it makes his little bath area look neat and fresh</t>
         </is>
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>DR_DUDU</t>
+          <t>Fufuzoie</t>
         </is>
       </c>
       <c r="D278" s="4" t="n">
@@ -4942,97 +4950,97 @@
       </c>
     </row>
     <row r="279">
-      <c r="B279" s="7" t="inlineStr">
-        <is>
-          <t>pure white</t>
-        </is>
-      </c>
-      <c r="C279" s="8" t="inlineStr">
-        <is>
-          <t>JFWOD</t>
-        </is>
-      </c>
-      <c r="D279" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E279" s="5">
-        <f>SUM(D279:D282)</f>
-        <v/>
+      <c r="B279" s="3" t="inlineStr">
+        <is>
+          <t>This is a nice white sand that is very low dust</t>
+        </is>
+      </c>
+      <c r="C279" s="4" t="inlineStr">
+        <is>
+          <t>Fufuzoie</t>
+        </is>
+      </c>
+      <c r="D279" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="280">
-      <c r="B280" s="7" t="inlineStr">
-        <is>
-          <t>Clean, and pretty sand</t>
-        </is>
-      </c>
-      <c r="C280" s="8" t="inlineStr">
-        <is>
-          <t>JFWOD</t>
-        </is>
-      </c>
-      <c r="D280" s="8" t="n">
+      <c r="B280" s="3" t="inlineStr">
+        <is>
+          <t>The brown color looks natural and blends well with most enclosure setups</t>
+        </is>
+      </c>
+      <c r="C280" s="4" t="inlineStr">
+        <is>
+          <t>Fufuzoie</t>
+        </is>
+      </c>
+      <c r="D280" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="281">
-      <c r="B281" s="7" t="inlineStr">
-        <is>
-          <t>I like that it looks more natural</t>
-        </is>
-      </c>
-      <c r="C281" s="8" t="inlineStr">
-        <is>
-          <t>JFWOD</t>
-        </is>
-      </c>
-      <c r="D281" s="8" t="n">
+      <c r="B281" s="3" t="inlineStr">
+        <is>
+          <t>the natural beige color also looks cleaner in the cage than artificially colored alternatives</t>
+        </is>
+      </c>
+      <c r="C281" s="4" t="inlineStr">
+        <is>
+          <t>Fufuzoie</t>
+        </is>
+      </c>
+      <c r="D281" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="282">
       <c r="B282" s="7" t="inlineStr">
         <is>
-          <t>It's white, clean, dense sand</t>
+          <t>Looks pretty</t>
         </is>
       </c>
       <c r="C282" s="8" t="inlineStr">
         <is>
-          <t>JFWOD</t>
+          <t>BUCATSTATE</t>
         </is>
       </c>
       <c r="D282" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="E282" s="5">
+        <f>SUM(D282:D282)</f>
+        <v/>
       </c>
     </row>
     <row r="283">
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>color blends well with the rest of his enclosure</t>
+          <t>It is white sand very, very fine</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>Fufuzoie</t>
+          <t>Hamiledyi</t>
         </is>
       </c>
       <c r="D283" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E283" s="5">
-        <f>SUM(D283:D287)</f>
+        <f>SUM(D283:D284)</f>
         <v/>
       </c>
     </row>
     <row r="284">
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>how bright white it is because it makes his little bath area look neat and fresh</t>
+          <t>Clean, and pretty sand</t>
         </is>
       </c>
       <c r="C284" s="4" t="inlineStr">
         <is>
-          <t>Fufuzoie</t>
+          <t>Hamiledyi</t>
         </is>
       </c>
       <c r="D284" s="4" t="n">
@@ -5040,174 +5048,174 @@
       </c>
     </row>
     <row r="285">
-      <c r="B285" s="3" t="inlineStr">
-        <is>
-          <t>This is a nice white sand that is very low dust</t>
-        </is>
-      </c>
-      <c r="C285" s="4" t="inlineStr">
-        <is>
-          <t>Fufuzoie</t>
-        </is>
-      </c>
-      <c r="D285" s="4" t="n">
-        <v>1</v>
+      <c r="B285" s="7" t="inlineStr">
+        <is>
+          <t>Clean, and pretty sand</t>
+        </is>
+      </c>
+      <c r="C285" s="8" t="inlineStr">
+        <is>
+          <t>Sukh</t>
+        </is>
+      </c>
+      <c r="D285" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E285" s="5">
+        <f>SUM(D285:D286)</f>
+        <v/>
       </c>
     </row>
     <row r="286">
-      <c r="B286" s="3" t="inlineStr">
-        <is>
-          <t>The brown color looks natural and blends well with most enclosure setups</t>
-        </is>
-      </c>
-      <c r="C286" s="4" t="inlineStr">
-        <is>
-          <t>Fufuzoie</t>
-        </is>
-      </c>
-      <c r="D286" s="4" t="n">
+      <c r="B286" s="7" t="inlineStr">
+        <is>
+          <t>it looks great</t>
+        </is>
+      </c>
+      <c r="C286" s="8" t="inlineStr">
+        <is>
+          <t>Sukh</t>
+        </is>
+      </c>
+      <c r="D286" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>No Odor/Unscented</t>
+        </is>
+      </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>the natural beige color also looks cleaner in the cage than artificially colored alternatives</t>
+          <t>No smell</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>Fufuzoie</t>
+          <t>JFWOD</t>
         </is>
       </c>
       <c r="D287" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="E287" s="5">
+        <f>SUM(D287:D288)</f>
+        <v/>
+      </c>
+      <c r="F287" s="6">
+        <f>SUM(E287:E301)</f>
+        <v/>
       </c>
     </row>
     <row r="288">
-      <c r="B288" s="7" t="inlineStr">
-        <is>
-          <t>Looks pretty</t>
-        </is>
-      </c>
-      <c r="C288" s="8" t="inlineStr">
-        <is>
-          <t>BUCATSTATE</t>
-        </is>
-      </c>
-      <c r="D288" s="8" t="n">
+      <c r="B288" s="3" t="inlineStr">
+        <is>
+          <t>No odor or texture issues</t>
+        </is>
+      </c>
+      <c r="C288" s="4" t="inlineStr">
+        <is>
+          <t>JFWOD</t>
+        </is>
+      </c>
+      <c r="D288" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="B289" s="7" t="inlineStr">
+        <is>
+          <t>No smell</t>
+        </is>
+      </c>
+      <c r="C289" s="8" t="inlineStr">
+        <is>
+          <t>DR_DUDU</t>
+        </is>
+      </c>
+      <c r="D289" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E288" s="5">
-        <f>SUM(D288:D288)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="289">
-      <c r="B289" s="3" t="inlineStr">
-        <is>
-          <t>It is white sand very, very fine</t>
-        </is>
-      </c>
-      <c r="C289" s="4" t="inlineStr">
-        <is>
-          <t>Hamiledyi</t>
-        </is>
-      </c>
-      <c r="D289" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="E289" s="5">
-        <f>SUM(D289:D290)</f>
+        <f>SUM(D289:D291)</f>
         <v/>
       </c>
     </row>
     <row r="290">
-      <c r="B290" s="3" t="inlineStr">
-        <is>
-          <t>Clean, and pretty sand</t>
-        </is>
-      </c>
-      <c r="C290" s="4" t="inlineStr">
-        <is>
-          <t>Hamiledyi</t>
-        </is>
-      </c>
-      <c r="D290" s="4" t="n">
+      <c r="B290" s="7" t="inlineStr">
+        <is>
+          <t>The sand was odorless, clean, and perfect for my hamster.</t>
+        </is>
+      </c>
+      <c r="C290" s="8" t="inlineStr">
+        <is>
+          <t>DR_DUDU</t>
+        </is>
+      </c>
+      <c r="D290" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="291">
       <c r="B291" s="7" t="inlineStr">
         <is>
-          <t>Clean, and pretty sand</t>
+          <t>good quality—not too fine, not dusty, and has no odor</t>
         </is>
       </c>
       <c r="C291" s="8" t="inlineStr">
         <is>
+          <t>DR_DUDU</t>
+        </is>
+      </c>
+      <c r="D291" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="B292" s="3" t="inlineStr">
+        <is>
+          <t>No smell</t>
+        </is>
+      </c>
+      <c r="C292" s="4" t="inlineStr">
+        <is>
           <t>Sukh</t>
         </is>
       </c>
-      <c r="D291" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E291" s="5">
-        <f>SUM(D291:D292)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="292">
-      <c r="B292" s="7" t="inlineStr">
-        <is>
-          <t>it looks great</t>
-        </is>
-      </c>
-      <c r="C292" s="8" t="inlineStr">
+      <c r="D292" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E292" s="5">
+        <f>SUM(D292:D294)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="293">
+      <c r="B293" s="3" t="inlineStr">
+        <is>
+          <t>clean soft and odorless</t>
+        </is>
+      </c>
+      <c r="C293" s="4" t="inlineStr">
         <is>
           <t>Sukh</t>
         </is>
       </c>
-      <c r="D292" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" s="2" t="inlineStr">
-        <is>
-          <t>No Odor/Unscented</t>
-        </is>
-      </c>
-      <c r="B293" s="3" t="inlineStr">
-        <is>
-          <t>No smell</t>
-        </is>
-      </c>
-      <c r="C293" s="4" t="inlineStr">
-        <is>
-          <t>JFWOD</t>
-        </is>
-      </c>
       <c r="D293" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E293" s="5">
-        <f>SUM(D293:D294)</f>
-        <v/>
-      </c>
-      <c r="F293" s="6">
-        <f>SUM(E293:E307)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="294">
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>No odor or texture issues</t>
+          <t>The sand is soft, clean, and doesn't smell</t>
         </is>
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>JFWOD</t>
+          <t>Sukh</t>
         </is>
       </c>
       <c r="D294" s="4" t="n">
@@ -5222,11 +5230,11 @@
       </c>
       <c r="C295" s="8" t="inlineStr">
         <is>
-          <t>DR_DUDU</t>
+          <t>Fufuzoie</t>
         </is>
       </c>
       <c r="D295" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E295" s="5">
         <f>SUM(D295:D297)</f>
@@ -5236,12 +5244,12 @@
     <row r="296">
       <c r="B296" s="7" t="inlineStr">
         <is>
-          <t>The sand was odorless, clean, and perfect for my hamster.</t>
+          <t>unscented and appears very clean and even in coarseness</t>
         </is>
       </c>
       <c r="C296" s="8" t="inlineStr">
         <is>
-          <t>DR_DUDU</t>
+          <t>Fufuzoie</t>
         </is>
       </c>
       <c r="D296" s="8" t="n">
@@ -5251,12 +5259,12 @@
     <row r="297">
       <c r="B297" s="7" t="inlineStr">
         <is>
-          <t>good quality—not too fine, not dusty, and has no odor</t>
+          <t>The sand is dust-free and unscented</t>
         </is>
       </c>
       <c r="C297" s="8" t="inlineStr">
         <is>
-          <t>DR_DUDU</t>
+          <t>Fufuzoie</t>
         </is>
       </c>
       <c r="D297" s="8" t="n">
@@ -5271,26 +5279,26 @@
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>Sukh</t>
+          <t>BUCATSTATE</t>
         </is>
       </c>
       <c r="D298" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E298" s="5">
-        <f>SUM(D298:D300)</f>
+        <f>SUM(D298:D299)</f>
         <v/>
       </c>
     </row>
     <row r="299">
       <c r="B299" s="3" t="inlineStr">
         <is>
-          <t>clean soft and odorless</t>
+          <t>The smell from the flowers is not noticeable</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>Sukh</t>
+          <t>BUCATSTATE</t>
         </is>
       </c>
       <c r="D299" s="4" t="n">
@@ -5298,356 +5306,356 @@
       </c>
     </row>
     <row r="300">
-      <c r="B300" s="3" t="inlineStr">
-        <is>
-          <t>The sand is soft, clean, and doesn't smell</t>
-        </is>
-      </c>
-      <c r="C300" s="4" t="inlineStr">
-        <is>
-          <t>Sukh</t>
-        </is>
-      </c>
-      <c r="D300" s="4" t="n">
-        <v>1</v>
+      <c r="B300" s="7" t="inlineStr">
+        <is>
+          <t>No smell</t>
+        </is>
+      </c>
+      <c r="C300" s="8" t="inlineStr">
+        <is>
+          <t>Hamiledyi</t>
+        </is>
+      </c>
+      <c r="D300" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E300" s="5">
+        <f>SUM(D300:D301)</f>
+        <v/>
       </c>
     </row>
     <row r="301">
       <c r="B301" s="7" t="inlineStr">
         <is>
-          <t>No smell</t>
+          <t>Sand has great texture and no scent</t>
         </is>
       </c>
       <c r="C301" s="8" t="inlineStr">
         <is>
+          <t>Hamiledyi</t>
+        </is>
+      </c>
+      <c r="D301" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>Convenient Pour Spout</t>
+        </is>
+      </c>
+      <c r="B302" s="3" t="inlineStr">
+        <is>
+          <t>The pour spout is super convenient</t>
+        </is>
+      </c>
+      <c r="C302" s="4" t="inlineStr">
+        <is>
           <t>Fufuzoie</t>
         </is>
       </c>
-      <c r="D301" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E301" s="5">
-        <f>SUM(D301:D303)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="302">
-      <c r="B302" s="7" t="inlineStr">
-        <is>
-          <t>unscented and appears very clean and even in coarseness</t>
-        </is>
-      </c>
-      <c r="C302" s="8" t="inlineStr">
+      <c r="D302" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E302" s="5">
+        <f>SUM(D302:D304)</f>
+        <v/>
+      </c>
+      <c r="F302" s="6">
+        <f>SUM(E302:E309)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="303">
+      <c r="B303" s="3" t="inlineStr">
+        <is>
+          <t>spout that makes pouring easier without spillage</t>
+        </is>
+      </c>
+      <c r="C303" s="4" t="inlineStr">
         <is>
           <t>Fufuzoie</t>
         </is>
       </c>
-      <c r="D302" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="B303" s="7" t="inlineStr">
-        <is>
-          <t>The sand is dust-free and unscented</t>
-        </is>
-      </c>
-      <c r="C303" s="8" t="inlineStr">
-        <is>
-          <t>Fufuzoie</t>
-        </is>
-      </c>
-      <c r="D303" s="8" t="n">
-        <v>1</v>
+      <c r="D303" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="304">
       <c r="B304" s="3" t="inlineStr">
         <is>
-          <t>No smell</t>
+          <t>thick plastic bag like container with a twist off spout</t>
         </is>
       </c>
       <c r="C304" s="4" t="inlineStr">
         <is>
+          <t>Fufuzoie</t>
+        </is>
+      </c>
+      <c r="D304" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="B305" s="7" t="inlineStr">
+        <is>
+          <t>The pour spout is super convenient</t>
+        </is>
+      </c>
+      <c r="C305" s="8" t="inlineStr">
+        <is>
           <t>BUCATSTATE</t>
         </is>
       </c>
-      <c r="D304" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E304" s="5">
-        <f>SUM(D304:D305)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="305">
-      <c r="B305" s="3" t="inlineStr">
-        <is>
-          <t>The smell from the flowers is not noticeable</t>
-        </is>
-      </c>
-      <c r="C305" s="4" t="inlineStr">
-        <is>
-          <t>BUCATSTATE</t>
-        </is>
-      </c>
-      <c r="D305" s="4" t="n">
-        <v>1</v>
+      <c r="D305" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E305" s="5">
+        <f>SUM(D305:D309)</f>
+        <v/>
       </c>
     </row>
     <row r="306">
       <c r="B306" s="7" t="inlineStr">
         <is>
-          <t>No smell</t>
+          <t>I DO like the packaging, easy to pour, and I like the little "scoopers" it comes with</t>
         </is>
       </c>
       <c r="C306" s="8" t="inlineStr">
         <is>
-          <t>Hamiledyi</t>
+          <t>BUCATSTATE</t>
         </is>
       </c>
       <c r="D306" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E306" s="5">
-        <f>SUM(D306:D307)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="307">
       <c r="B307" s="7" t="inlineStr">
         <is>
-          <t>Sand has great texture and no scent</t>
+          <t>spout that makes pouring easier without spillage</t>
         </is>
       </c>
       <c r="C307" s="8" t="inlineStr">
         <is>
-          <t>Hamiledyi</t>
+          <t>BUCATSTATE</t>
         </is>
       </c>
       <c r="D307" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="2" t="inlineStr">
-        <is>
-          <t>Convenient Pour Spout</t>
-        </is>
-      </c>
-      <c r="B308" s="3" t="inlineStr">
-        <is>
-          <t>The pour spout is super convenient</t>
-        </is>
-      </c>
-      <c r="C308" s="4" t="inlineStr">
-        <is>
-          <t>Fufuzoie</t>
-        </is>
-      </c>
-      <c r="D308" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E308" s="5">
-        <f>SUM(D308:D310)</f>
-        <v/>
-      </c>
-      <c r="F308" s="6">
-        <f>SUM(E308:E315)</f>
-        <v/>
+      <c r="B308" s="7" t="inlineStr">
+        <is>
+          <t>it came with the pour spout and a little shovel</t>
+        </is>
+      </c>
+      <c r="C308" s="8" t="inlineStr">
+        <is>
+          <t>BUCATSTATE</t>
+        </is>
+      </c>
+      <c r="D308" s="8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="309">
-      <c r="B309" s="3" t="inlineStr">
-        <is>
-          <t>spout that makes pouring easier without spillage</t>
-        </is>
-      </c>
-      <c r="C309" s="4" t="inlineStr">
-        <is>
-          <t>Fufuzoie</t>
-        </is>
-      </c>
-      <c r="D309" s="4" t="n">
-        <v>5</v>
+      <c r="B309" s="7" t="inlineStr">
+        <is>
+          <t>the spout on the bag makes it really easy to pour into a sand bath without making a mess and it comes with a free scooper</t>
+        </is>
+      </c>
+      <c r="C309" s="8" t="inlineStr">
+        <is>
+          <t>BUCATSTATE</t>
+        </is>
+      </c>
+      <c r="D309" s="8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>Good Clumping</t>
+        </is>
+      </c>
       <c r="B310" s="3" t="inlineStr">
         <is>
-          <t>thick plastic bag like container with a twist off spout</t>
+          <t>It clumps good</t>
         </is>
       </c>
       <c r="C310" s="4" t="inlineStr">
         <is>
-          <t>Fufuzoie</t>
+          <t>DR_DUDU</t>
         </is>
       </c>
       <c r="D310" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="E310" s="5">
+        <f>SUM(D310:D315)</f>
+        <v/>
+      </c>
+      <c r="F310" s="6">
+        <f>SUM(E310:E325)</f>
+        <v/>
+      </c>
     </row>
     <row r="311">
-      <c r="B311" s="7" t="inlineStr">
-        <is>
-          <t>The pour spout is super convenient</t>
-        </is>
-      </c>
-      <c r="C311" s="8" t="inlineStr">
-        <is>
-          <t>BUCATSTATE</t>
-        </is>
-      </c>
-      <c r="D311" s="8" t="n">
+      <c r="B311" s="3" t="inlineStr">
+        <is>
+          <t>It absorbs well, so it's easy to sift out the clumps</t>
+        </is>
+      </c>
+      <c r="C311" s="4" t="inlineStr">
+        <is>
+          <t>DR_DUDU</t>
+        </is>
+      </c>
+      <c r="D311" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="B312" s="3" t="inlineStr">
+        <is>
+          <t>it holds together so its easier to clean</t>
+        </is>
+      </c>
+      <c r="C312" s="4" t="inlineStr">
+        <is>
+          <t>DR_DUDU</t>
+        </is>
+      </c>
+      <c r="D312" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="B313" s="3" t="inlineStr">
+        <is>
+          <t>clumps the pee very well</t>
+        </is>
+      </c>
+      <c r="C313" s="4" t="inlineStr">
+        <is>
+          <t>DR_DUDU</t>
+        </is>
+      </c>
+      <c r="D313" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="B314" s="3" t="inlineStr">
+        <is>
+          <t>It doesn't spread throughout</t>
+        </is>
+      </c>
+      <c r="C314" s="4" t="inlineStr">
+        <is>
+          <t>DR_DUDU</t>
+        </is>
+      </c>
+      <c r="D314" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="B315" s="3" t="inlineStr">
+        <is>
+          <t>so easy to scoop out the clump of pee</t>
+        </is>
+      </c>
+      <c r="C315" s="4" t="inlineStr">
+        <is>
+          <t>DR_DUDU</t>
+        </is>
+      </c>
+      <c r="D315" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="B316" s="7" t="inlineStr">
+        <is>
+          <t>It clumps good</t>
+        </is>
+      </c>
+      <c r="C316" s="8" t="inlineStr">
+        <is>
+          <t>JFWOD</t>
+        </is>
+      </c>
+      <c r="D316" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E311" s="5">
-        <f>SUM(D311:D315)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="312">
-      <c r="B312" s="7" t="inlineStr">
-        <is>
-          <t>I DO like the packaging, easy to pour, and I like the little "scoopers" it comes with</t>
-        </is>
-      </c>
-      <c r="C312" s="8" t="inlineStr">
-        <is>
-          <t>BUCATSTATE</t>
-        </is>
-      </c>
-      <c r="D312" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="B313" s="7" t="inlineStr">
-        <is>
-          <t>spout that makes pouring easier without spillage</t>
-        </is>
-      </c>
-      <c r="C313" s="8" t="inlineStr">
-        <is>
-          <t>BUCATSTATE</t>
-        </is>
-      </c>
-      <c r="D313" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="B314" s="7" t="inlineStr">
-        <is>
-          <t>it came with the pour spout and a little shovel</t>
-        </is>
-      </c>
-      <c r="C314" s="8" t="inlineStr">
-        <is>
-          <t>BUCATSTATE</t>
-        </is>
-      </c>
-      <c r="D314" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="B315" s="7" t="inlineStr">
-        <is>
-          <t>the spout on the bag makes it really easy to pour into a sand bath without making a mess and it comes with a free scooper</t>
-        </is>
-      </c>
-      <c r="C315" s="8" t="inlineStr">
-        <is>
-          <t>BUCATSTATE</t>
-        </is>
-      </c>
-      <c r="D315" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" s="2" t="inlineStr">
-        <is>
-          <t>Good Clumping</t>
-        </is>
-      </c>
-      <c r="B316" s="3" t="inlineStr">
-        <is>
-          <t>It clumps good</t>
-        </is>
-      </c>
-      <c r="C316" s="4" t="inlineStr">
-        <is>
-          <t>DR_DUDU</t>
-        </is>
-      </c>
-      <c r="D316" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="E316" s="5">
-        <f>SUM(D316:D321)</f>
-        <v/>
-      </c>
-      <c r="F316" s="6">
-        <f>SUM(E316:E331)</f>
+        <f>SUM(D316:D318)</f>
         <v/>
       </c>
     </row>
     <row r="317">
-      <c r="B317" s="3" t="inlineStr">
-        <is>
-          <t>It absorbs well, so it's easy to sift out the clumps</t>
-        </is>
-      </c>
-      <c r="C317" s="4" t="inlineStr">
-        <is>
-          <t>DR_DUDU</t>
-        </is>
-      </c>
-      <c r="D317" s="4" t="n">
+      <c r="B317" s="7" t="inlineStr">
+        <is>
+          <t>so easy to scoop out the clump of pee</t>
+        </is>
+      </c>
+      <c r="C317" s="8" t="inlineStr">
+        <is>
+          <t>JFWOD</t>
+        </is>
+      </c>
+      <c r="D317" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="318">
-      <c r="B318" s="3" t="inlineStr">
-        <is>
-          <t>it holds together so its easier to clean</t>
-        </is>
-      </c>
-      <c r="C318" s="4" t="inlineStr">
-        <is>
-          <t>DR_DUDU</t>
-        </is>
-      </c>
-      <c r="D318" s="4" t="n">
+      <c r="B318" s="7" t="inlineStr">
+        <is>
+          <t>It clumped up well, making it easy to find his little "remembrances"</t>
+        </is>
+      </c>
+      <c r="C318" s="8" t="inlineStr">
+        <is>
+          <t>JFWOD</t>
+        </is>
+      </c>
+      <c r="D318" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="319">
       <c r="B319" s="3" t="inlineStr">
         <is>
-          <t>clumps the pee very well</t>
+          <t>It clumps good</t>
         </is>
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>DR_DUDU</t>
+          <t>BUCATSTATE</t>
         </is>
       </c>
       <c r="D319" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="E319" s="5">
+        <f>SUM(D319:D320)</f>
+        <v/>
       </c>
     </row>
     <row r="320">
       <c r="B320" s="3" t="inlineStr">
         <is>
-          <t>It doesn't spread throughout</t>
+          <t>it does make noticeable clumps that can be scooped out with the included scooper</t>
         </is>
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>DR_DUDU</t>
+          <t>BUCATSTATE</t>
         </is>
       </c>
       <c r="D320" s="4" t="n">
@@ -5655,48 +5663,48 @@
       </c>
     </row>
     <row r="321">
-      <c r="B321" s="3" t="inlineStr">
-        <is>
-          <t>so easy to scoop out the clump of pee</t>
-        </is>
-      </c>
-      <c r="C321" s="4" t="inlineStr">
-        <is>
-          <t>DR_DUDU</t>
-        </is>
-      </c>
-      <c r="D321" s="4" t="n">
-        <v>1</v>
+      <c r="B321" s="7" t="inlineStr">
+        <is>
+          <t>It clumps good</t>
+        </is>
+      </c>
+      <c r="C321" s="8" t="inlineStr">
+        <is>
+          <t>Fufuzoie</t>
+        </is>
+      </c>
+      <c r="D321" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E321" s="5">
+        <f>SUM(D321:D324)</f>
+        <v/>
       </c>
     </row>
     <row r="322">
       <c r="B322" s="7" t="inlineStr">
         <is>
-          <t>It clumps good</t>
+          <t>clumps the pee very well</t>
         </is>
       </c>
       <c r="C322" s="8" t="inlineStr">
         <is>
-          <t>JFWOD</t>
+          <t>Fufuzoie</t>
         </is>
       </c>
       <c r="D322" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E322" s="5">
-        <f>SUM(D322:D324)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="323">
       <c r="B323" s="7" t="inlineStr">
         <is>
-          <t>so easy to scoop out the clump of pee</t>
+          <t>The sand clumps well and is easy to remove when we clean it out daily</t>
         </is>
       </c>
       <c r="C323" s="8" t="inlineStr">
         <is>
-          <t>JFWOD</t>
+          <t>Fufuzoie</t>
         </is>
       </c>
       <c r="D323" s="8" t="n">
@@ -5706,12 +5714,12 @@
     <row r="324">
       <c r="B324" s="7" t="inlineStr">
         <is>
-          <t>It clumped up well, making it easy to find his little "remembrances"</t>
+          <t>Doesn't clump on their feathers</t>
         </is>
       </c>
       <c r="C324" s="8" t="inlineStr">
         <is>
-          <t>JFWOD</t>
+          <t>Fufuzoie</t>
         </is>
       </c>
       <c r="D324" s="8" t="n">
@@ -5721,330 +5729,347 @@
     <row r="325">
       <c r="B325" s="3" t="inlineStr">
         <is>
-          <t>It clumps good</t>
+          <t>Clumps amazing</t>
         </is>
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
+          <t>Sukh</t>
+        </is>
+      </c>
+      <c r="D325" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E325" s="5">
+        <f>SUM(D325:D325)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>Handy Container</t>
+        </is>
+      </c>
+      <c r="B326" s="3" t="inlineStr">
+        <is>
+          <t>The bag it comes in is nice and thick so it won't break easily</t>
+        </is>
+      </c>
+      <c r="C326" s="4" t="inlineStr">
+        <is>
           <t>BUCATSTATE</t>
         </is>
       </c>
-      <c r="D325" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E325" s="5">
-        <f>SUM(D325:D326)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="326">
-      <c r="B326" s="3" t="inlineStr">
-        <is>
-          <t>it does make noticeable clumps that can be scooped out with the included scooper</t>
-        </is>
-      </c>
-      <c r="C326" s="4" t="inlineStr">
+      <c r="D326" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E326" s="5">
+        <f>SUM(D326:D331)</f>
+        <v/>
+      </c>
+      <c r="F326" s="6">
+        <f>SUM(E326:E341)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="327">
+      <c r="B327" s="3" t="inlineStr">
+        <is>
+          <t>the container it comes in makes using the sand super easy</t>
+        </is>
+      </c>
+      <c r="C327" s="4" t="inlineStr">
         <is>
           <t>BUCATSTATE</t>
         </is>
       </c>
-      <c r="D326" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="B327" s="7" t="inlineStr">
-        <is>
-          <t>It clumps good</t>
-        </is>
-      </c>
-      <c r="C327" s="8" t="inlineStr">
-        <is>
-          <t>Fufuzoie</t>
-        </is>
-      </c>
-      <c r="D327" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E327" s="5">
-        <f>SUM(D327:D330)</f>
-        <v/>
+      <c r="D327" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="328">
-      <c r="B328" s="7" t="inlineStr">
-        <is>
-          <t>clumps the pee very well</t>
-        </is>
-      </c>
-      <c r="C328" s="8" t="inlineStr">
-        <is>
-          <t>Fufuzoie</t>
-        </is>
-      </c>
-      <c r="D328" s="8" t="n">
+      <c r="B328" s="3" t="inlineStr">
+        <is>
+          <t>There is so little waste of unsoiled sand</t>
+        </is>
+      </c>
+      <c r="C328" s="4" t="inlineStr">
+        <is>
+          <t>BUCATSTATE</t>
+        </is>
+      </c>
+      <c r="D328" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="329">
-      <c r="B329" s="7" t="inlineStr">
-        <is>
-          <t>The sand clumps well and is easy to remove when we clean it out daily</t>
-        </is>
-      </c>
-      <c r="C329" s="8" t="inlineStr">
-        <is>
-          <t>Fufuzoie</t>
-        </is>
-      </c>
-      <c r="D329" s="8" t="n">
+      <c r="B329" s="3" t="inlineStr">
+        <is>
+          <t>It's a small bag which makes it excellent for their dust bath spots and indoor shelf storage</t>
+        </is>
+      </c>
+      <c r="C329" s="4" t="inlineStr">
+        <is>
+          <t>BUCATSTATE</t>
+        </is>
+      </c>
+      <c r="D329" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="330">
-      <c r="B330" s="7" t="inlineStr">
-        <is>
-          <t>Doesn't clump on their feathers</t>
-        </is>
-      </c>
-      <c r="C330" s="8" t="inlineStr">
-        <is>
-          <t>Fufuzoie</t>
-        </is>
-      </c>
-      <c r="D330" s="8" t="n">
+      <c r="B330" s="3" t="inlineStr">
+        <is>
+          <t>Handle for carry and grip</t>
+        </is>
+      </c>
+      <c r="C330" s="4" t="inlineStr">
+        <is>
+          <t>BUCATSTATE</t>
+        </is>
+      </c>
+      <c r="D330" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="331">
       <c r="B331" s="3" t="inlineStr">
         <is>
-          <t>Clumps amazing</t>
+          <t>my mouse knows the difference between his litter box and sand bath container</t>
         </is>
       </c>
       <c r="C331" s="4" t="inlineStr">
         <is>
-          <t>Sukh</t>
+          <t>BUCATSTATE</t>
         </is>
       </c>
       <c r="D331" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E331" s="5">
-        <f>SUM(D331:D331)</f>
-        <v/>
-      </c>
     </row>
     <row r="332">
-      <c r="A332" s="2" t="inlineStr">
-        <is>
-          <t>Handy Container</t>
-        </is>
-      </c>
-      <c r="B332" s="3" t="inlineStr">
-        <is>
-          <t>The bag it comes in is nice and thick so it won't break easily</t>
-        </is>
-      </c>
-      <c r="C332" s="4" t="inlineStr">
-        <is>
-          <t>BUCATSTATE</t>
-        </is>
-      </c>
-      <c r="D332" s="4" t="n">
-        <v>2</v>
+      <c r="B332" s="7" t="inlineStr">
+        <is>
+          <t>It has a pour spout! What a great idea to be able to dispense what you need and then close it up again</t>
+        </is>
+      </c>
+      <c r="C332" s="8" t="inlineStr">
+        <is>
+          <t>Fufuzoie</t>
+        </is>
+      </c>
+      <c r="D332" s="8" t="n">
+        <v>3</v>
       </c>
       <c r="E332" s="5">
-        <f>SUM(D332:D337)</f>
-        <v/>
-      </c>
-      <c r="F332" s="6">
-        <f>SUM(E332:E347)</f>
+        <f>SUM(D332:D336)</f>
         <v/>
       </c>
     </row>
     <row r="333">
-      <c r="B333" s="3" t="inlineStr">
+      <c r="B333" s="7" t="inlineStr">
+        <is>
+          <t>The bag is a good size for regular use</t>
+        </is>
+      </c>
+      <c r="C333" s="8" t="inlineStr">
+        <is>
+          <t>Fufuzoie</t>
+        </is>
+      </c>
+      <c r="D333" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="B334" s="7" t="inlineStr">
         <is>
           <t>the container it comes in makes using the sand super easy</t>
         </is>
       </c>
-      <c r="C333" s="4" t="inlineStr">
-        <is>
-          <t>BUCATSTATE</t>
-        </is>
-      </c>
-      <c r="D333" s="4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="B334" s="3" t="inlineStr">
-        <is>
-          <t>There is so little waste of unsoiled sand</t>
-        </is>
-      </c>
-      <c r="C334" s="4" t="inlineStr">
-        <is>
-          <t>BUCATSTATE</t>
-        </is>
-      </c>
-      <c r="D334" s="4" t="n">
+      <c r="C334" s="8" t="inlineStr">
+        <is>
+          <t>Fufuzoie</t>
+        </is>
+      </c>
+      <c r="D334" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="335">
-      <c r="B335" s="3" t="inlineStr">
-        <is>
-          <t>It's a small bag which makes it excellent for their dust bath spots and indoor shelf storage</t>
-        </is>
-      </c>
-      <c r="C335" s="4" t="inlineStr">
-        <is>
-          <t>BUCATSTATE</t>
-        </is>
-      </c>
-      <c r="D335" s="4" t="n">
+      <c r="B335" s="7" t="inlineStr">
+        <is>
+          <t>The spout design lets you pour a controlled amount directly into the bath container without dumping half the bag at once</t>
+        </is>
+      </c>
+      <c r="C335" s="8" t="inlineStr">
+        <is>
+          <t>Fufuzoie</t>
+        </is>
+      </c>
+      <c r="D335" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="336">
-      <c r="B336" s="3" t="inlineStr">
-        <is>
-          <t>Handle for carry and grip</t>
-        </is>
-      </c>
-      <c r="C336" s="4" t="inlineStr">
-        <is>
-          <t>BUCATSTATE</t>
-        </is>
-      </c>
-      <c r="D336" s="4" t="n">
+      <c r="B336" s="7" t="inlineStr">
+        <is>
+          <t>comes in a really nice package with a resealable spout on it that allows easy pouring into small spaces</t>
+        </is>
+      </c>
+      <c r="C336" s="8" t="inlineStr">
+        <is>
+          <t>Fufuzoie</t>
+        </is>
+      </c>
+      <c r="D336" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="337">
       <c r="B337" s="3" t="inlineStr">
         <is>
-          <t>my mouse knows the difference between his litter box and sand bath container</t>
+          <t>The bag it comes in is nice and thick so it won't break easily</t>
         </is>
       </c>
       <c r="C337" s="4" t="inlineStr">
         <is>
-          <t>BUCATSTATE</t>
+          <t>DR_DUDU</t>
         </is>
       </c>
       <c r="D337" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="E337" s="5">
+        <f>SUM(D337:D338)</f>
+        <v/>
+      </c>
     </row>
     <row r="338">
-      <c r="B338" s="7" t="inlineStr">
-        <is>
-          <t>It has a pour spout! What a great idea to be able to dispense what you need and then close it up again</t>
-        </is>
-      </c>
-      <c r="C338" s="8" t="inlineStr">
-        <is>
-          <t>Fufuzoie</t>
-        </is>
-      </c>
-      <c r="D338" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E338" s="5">
-        <f>SUM(D338:D342)</f>
-        <v/>
+      <c r="B338" s="3" t="inlineStr">
+        <is>
+          <t>long ago there were issues with the bags leaking, but that never seems to happen anymore</t>
+        </is>
+      </c>
+      <c r="C338" s="4" t="inlineStr">
+        <is>
+          <t>DR_DUDU</t>
+        </is>
+      </c>
+      <c r="D338" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="339">
       <c r="B339" s="7" t="inlineStr">
         <is>
-          <t>The bag is a good size for regular use</t>
+          <t>The bag it comes in is nice and thick so it won't break easily</t>
         </is>
       </c>
       <c r="C339" s="8" t="inlineStr">
         <is>
-          <t>Fufuzoie</t>
+          <t>Hamiledyi</t>
         </is>
       </c>
       <c r="D339" s="8" t="n">
         <v>1</v>
       </c>
+      <c r="E339" s="5">
+        <f>SUM(D339:D339)</f>
+        <v/>
+      </c>
     </row>
     <row r="340">
-      <c r="B340" s="7" t="inlineStr">
-        <is>
-          <t>the container it comes in makes using the sand super easy</t>
-        </is>
-      </c>
-      <c r="C340" s="8" t="inlineStr">
-        <is>
-          <t>Fufuzoie</t>
-        </is>
-      </c>
-      <c r="D340" s="8" t="n">
-        <v>1</v>
+      <c r="B340" s="3" t="inlineStr">
+        <is>
+          <t>The bag it comes in is nice and thick so it won't break easily</t>
+        </is>
+      </c>
+      <c r="C340" s="4" t="inlineStr">
+        <is>
+          <t>JFWOD</t>
+        </is>
+      </c>
+      <c r="D340" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E340" s="5">
+        <f>SUM(D340:D340)</f>
+        <v/>
       </c>
     </row>
     <row r="341">
       <c r="B341" s="7" t="inlineStr">
         <is>
-          <t>The spout design lets you pour a controlled amount directly into the bath container without dumping half the bag at once</t>
+          <t>package arrived in good condition - no tears or spills</t>
         </is>
       </c>
       <c r="C341" s="8" t="inlineStr">
         <is>
-          <t>Fufuzoie</t>
+          <t>Sukh</t>
         </is>
       </c>
       <c r="D341" s="8" t="n">
         <v>1</v>
       </c>
+      <c r="E341" s="5">
+        <f>SUM(D341:D341)</f>
+        <v/>
+      </c>
     </row>
     <row r="342">
-      <c r="B342" s="7" t="inlineStr">
-        <is>
-          <t>comes in a really nice package with a resealable spout on it that allows easy pouring into small spaces</t>
-        </is>
-      </c>
-      <c r="C342" s="8" t="inlineStr">
-        <is>
-          <t>Fufuzoie</t>
-        </is>
-      </c>
-      <c r="D342" s="8" t="n">
-        <v>1</v>
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>Long Lasting</t>
+        </is>
+      </c>
+      <c r="B342" s="3" t="inlineStr">
+        <is>
+          <t>lasts a long time</t>
+        </is>
+      </c>
+      <c r="C342" s="4" t="inlineStr">
+        <is>
+          <t>JFWOD</t>
+        </is>
+      </c>
+      <c r="D342" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E342" s="5">
+        <f>SUM(D342:D345)</f>
+        <v/>
+      </c>
+      <c r="F342" s="6">
+        <f>SUM(E342:E352)</f>
+        <v/>
       </c>
     </row>
     <row r="343">
       <c r="B343" s="3" t="inlineStr">
         <is>
-          <t>The bag it comes in is nice and thick so it won't break easily</t>
+          <t>Should last a month or more</t>
         </is>
       </c>
       <c r="C343" s="4" t="inlineStr">
         <is>
-          <t>DR_DUDU</t>
+          <t>JFWOD</t>
         </is>
       </c>
       <c r="D343" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="E343" s="5">
-        <f>SUM(D343:D344)</f>
-        <v/>
       </c>
     </row>
     <row r="344">
       <c r="B344" s="3" t="inlineStr">
         <is>
-          <t>long ago there were issues with the bags leaking, but that never seems to happen anymore</t>
+          <t>He bag has lasted us a few months (about 3-4h and we still have some).</t>
         </is>
       </c>
       <c r="C344" s="4" t="inlineStr">
         <is>
-          <t>DR_DUDU</t>
+          <t>JFWOD</t>
         </is>
       </c>
       <c r="D344" s="4" t="n">
@@ -6052,68 +6077,55 @@
       </c>
     </row>
     <row r="345">
-      <c r="B345" s="7" t="inlineStr">
-        <is>
-          <t>The bag it comes in is nice and thick so it won't break easily</t>
-        </is>
-      </c>
-      <c r="C345" s="8" t="inlineStr">
-        <is>
-          <t>Hamiledyi</t>
-        </is>
-      </c>
-      <c r="D345" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E345" s="5">
-        <f>SUM(D345:D345)</f>
-        <v/>
+      <c r="B345" s="3" t="inlineStr">
+        <is>
+          <t>hefty quantity that'll last me several months</t>
+        </is>
+      </c>
+      <c r="C345" s="4" t="inlineStr">
+        <is>
+          <t>JFWOD</t>
+        </is>
+      </c>
+      <c r="D345" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="346">
-      <c r="B346" s="3" t="inlineStr">
-        <is>
-          <t>The bag it comes in is nice and thick so it won't break easily</t>
-        </is>
-      </c>
-      <c r="C346" s="4" t="inlineStr">
-        <is>
-          <t>JFWOD</t>
-        </is>
-      </c>
-      <c r="D346" s="4" t="n">
-        <v>1</v>
+      <c r="B346" s="7" t="inlineStr">
+        <is>
+          <t>lasts a long time</t>
+        </is>
+      </c>
+      <c r="C346" s="8" t="inlineStr">
+        <is>
+          <t>DR_DUDU</t>
+        </is>
+      </c>
+      <c r="D346" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="E346" s="5">
-        <f>SUM(D346:D346)</f>
+        <f>SUM(D346:D347)</f>
         <v/>
       </c>
     </row>
     <row r="347">
       <c r="B347" s="7" t="inlineStr">
         <is>
-          <t>package arrived in good condition - no tears or spills</t>
+          <t>Plenty of sand to last me longer than the 2 lb bag.</t>
         </is>
       </c>
       <c r="C347" s="8" t="inlineStr">
         <is>
-          <t>Sukh</t>
+          <t>DR_DUDU</t>
         </is>
       </c>
       <c r="D347" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E347" s="5">
-        <f>SUM(D347:D347)</f>
-        <v/>
-      </c>
     </row>
     <row r="348">
-      <c r="A348" s="2" t="inlineStr">
-        <is>
-          <t>Long Lasting</t>
-        </is>
-      </c>
       <c r="B348" s="3" t="inlineStr">
         <is>
           <t>lasts a long time</t>
@@ -6121,30 +6133,26 @@
       </c>
       <c r="C348" s="4" t="inlineStr">
         <is>
-          <t>JFWOD</t>
+          <t>Fufuzoie</t>
         </is>
       </c>
       <c r="D348" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E348" s="5">
-        <f>SUM(D348:D351)</f>
-        <v/>
-      </c>
-      <c r="F348" s="6">
-        <f>SUM(E348:E358)</f>
+        <f>SUM(D348:D349)</f>
         <v/>
       </c>
     </row>
     <row r="349">
       <c r="B349" s="3" t="inlineStr">
         <is>
-          <t>Should last a month or more</t>
+          <t>This helps keep the sand longer</t>
         </is>
       </c>
       <c r="C349" s="4" t="inlineStr">
         <is>
-          <t>JFWOD</t>
+          <t>Fufuzoie</t>
         </is>
       </c>
       <c r="D349" s="4" t="n">
@@ -6152,97 +6160,110 @@
       </c>
     </row>
     <row r="350">
-      <c r="B350" s="3" t="inlineStr">
-        <is>
-          <t>He bag has lasted us a few months (about 3-4h and we still have some).</t>
-        </is>
-      </c>
-      <c r="C350" s="4" t="inlineStr">
-        <is>
-          <t>JFWOD</t>
-        </is>
-      </c>
-      <c r="D350" s="4" t="n">
-        <v>1</v>
+      <c r="B350" s="7" t="inlineStr">
+        <is>
+          <t>lasts a long time</t>
+        </is>
+      </c>
+      <c r="C350" s="8" t="inlineStr">
+        <is>
+          <t>BUCATSTATE</t>
+        </is>
+      </c>
+      <c r="D350" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E350" s="5">
+        <f>SUM(D350:D351)</f>
+        <v/>
       </c>
     </row>
     <row r="351">
-      <c r="B351" s="3" t="inlineStr">
-        <is>
-          <t>hefty quantity that'll last me several months</t>
-        </is>
-      </c>
-      <c r="C351" s="4" t="inlineStr">
-        <is>
-          <t>JFWOD</t>
-        </is>
-      </c>
-      <c r="D351" s="4" t="n">
+      <c r="B351" s="7" t="inlineStr">
+        <is>
+          <t>6.6lbs is a great amount to use for months</t>
+        </is>
+      </c>
+      <c r="C351" s="8" t="inlineStr">
+        <is>
+          <t>BUCATSTATE</t>
+        </is>
+      </c>
+      <c r="D351" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="352">
-      <c r="B352" s="7" t="inlineStr">
+      <c r="B352" s="3" t="inlineStr">
         <is>
           <t>lasts a long time</t>
         </is>
       </c>
-      <c r="C352" s="8" t="inlineStr">
-        <is>
-          <t>DR_DUDU</t>
-        </is>
-      </c>
-      <c r="D352" s="8" t="n">
-        <v>5</v>
+      <c r="C352" s="4" t="inlineStr">
+        <is>
+          <t>Hamiledyi</t>
+        </is>
+      </c>
+      <c r="D352" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="E352" s="5">
-        <f>SUM(D352:D353)</f>
+        <f>SUM(D352:D352)</f>
         <v/>
       </c>
     </row>
     <row r="353">
-      <c r="B353" s="7" t="inlineStr">
-        <is>
-          <t>Plenty of sand to last me longer than the 2 lb bag.</t>
-        </is>
-      </c>
-      <c r="C353" s="8" t="inlineStr">
-        <is>
-          <t>DR_DUDU</t>
-        </is>
-      </c>
-      <c r="D353" s="8" t="n">
-        <v>1</v>
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>Neutralizes Odor Well</t>
+        </is>
+      </c>
+      <c r="B353" s="3" t="inlineStr">
+        <is>
+          <t>it neutralizes odor so well</t>
+        </is>
+      </c>
+      <c r="C353" s="4" t="inlineStr">
+        <is>
+          <t>JFWOD</t>
+        </is>
+      </c>
+      <c r="D353" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E353" s="5">
+        <f>SUM(D353:D356)</f>
+        <v/>
+      </c>
+      <c r="F353" s="6">
+        <f>SUM(E353:E363)</f>
+        <v/>
       </c>
     </row>
     <row r="354">
       <c r="B354" s="3" t="inlineStr">
         <is>
-          <t>lasts a long time</t>
+          <t>helps us keep the cage smelling not as bad a going longer between changes</t>
         </is>
       </c>
       <c r="C354" s="4" t="inlineStr">
         <is>
-          <t>Fufuzoie</t>
+          <t>JFWOD</t>
         </is>
       </c>
       <c r="D354" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E354" s="5">
-        <f>SUM(D354:D355)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="355">
       <c r="B355" s="3" t="inlineStr">
         <is>
-          <t>This helps keep the sand longer</t>
+          <t>Bedding stays much cleaner and smells much better longer</t>
         </is>
       </c>
       <c r="C355" s="4" t="inlineStr">
         <is>
-          <t>Fufuzoie</t>
+          <t>JFWOD</t>
         </is>
       </c>
       <c r="D355" s="4" t="n">
@@ -6250,95 +6271,82 @@
       </c>
     </row>
     <row r="356">
-      <c r="B356" s="7" t="inlineStr">
-        <is>
-          <t>lasts a long time</t>
-        </is>
-      </c>
-      <c r="C356" s="8" t="inlineStr">
-        <is>
-          <t>BUCATSTATE</t>
-        </is>
-      </c>
-      <c r="D356" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E356" s="5">
-        <f>SUM(D356:D357)</f>
-        <v/>
+      <c r="B356" s="3" t="inlineStr">
+        <is>
+          <t>helps us keep the cage smelling not as bad</t>
+        </is>
+      </c>
+      <c r="C356" s="4" t="inlineStr">
+        <is>
+          <t>JFWOD</t>
+        </is>
+      </c>
+      <c r="D356" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="357">
       <c r="B357" s="7" t="inlineStr">
         <is>
-          <t>6.6lbs is a great amount to use for months</t>
+          <t>it neutralizes odor so well</t>
         </is>
       </c>
       <c r="C357" s="8" t="inlineStr">
         <is>
-          <t>BUCATSTATE</t>
+          <t>DR_DUDU</t>
         </is>
       </c>
       <c r="D357" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="E357" s="5">
+        <f>SUM(D357:D357)</f>
+        <v/>
       </c>
     </row>
     <row r="358">
       <c r="B358" s="3" t="inlineStr">
         <is>
-          <t>lasts a long time</t>
+          <t>it neutralizes odor so well</t>
         </is>
       </c>
       <c r="C358" s="4" t="inlineStr">
         <is>
-          <t>Hamiledyi</t>
+          <t>Fufuzoie</t>
         </is>
       </c>
       <c r="D358" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E358" s="5">
-        <f>SUM(D358:D358)</f>
+        <f>SUM(D358:D360)</f>
         <v/>
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="2" t="inlineStr">
-        <is>
-          <t>Neutralizes Odor Well</t>
-        </is>
-      </c>
       <c r="B359" s="3" t="inlineStr">
         <is>
-          <t>it neutralizes odor so well</t>
+          <t>air within our hamsters habitat stays fresher a bit longer</t>
         </is>
       </c>
       <c r="C359" s="4" t="inlineStr">
         <is>
-          <t>JFWOD</t>
+          <t>Fufuzoie</t>
         </is>
       </c>
       <c r="D359" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E359" s="5">
-        <f>SUM(D359:D362)</f>
-        <v/>
-      </c>
-      <c r="F359" s="6">
-        <f>SUM(E359:E369)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="360">
       <c r="B360" s="3" t="inlineStr">
         <is>
-          <t>helps us keep the cage smelling not as bad a going longer between changes</t>
+          <t>help keep the cage fresher between cleanings</t>
         </is>
       </c>
       <c r="C360" s="4" t="inlineStr">
         <is>
-          <t>JFWOD</t>
+          <t>Fufuzoie</t>
         </is>
       </c>
       <c r="D360" s="4" t="n">
@@ -6346,48 +6354,56 @@
       </c>
     </row>
     <row r="361">
-      <c r="B361" s="3" t="inlineStr">
-        <is>
-          <t>Bedding stays much cleaner and smells much better longer</t>
-        </is>
-      </c>
-      <c r="C361" s="4" t="inlineStr">
-        <is>
-          <t>JFWOD</t>
-        </is>
-      </c>
-      <c r="D361" s="4" t="n">
-        <v>1</v>
+      <c r="B361" s="7" t="inlineStr">
+        <is>
+          <t>it neutralizes odor so well</t>
+        </is>
+      </c>
+      <c r="C361" s="8" t="inlineStr">
+        <is>
+          <t>Meow&amp;Woof</t>
+        </is>
+      </c>
+      <c r="D361" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E361" s="5">
+        <f>SUM(D361:D361)</f>
+        <v/>
       </c>
     </row>
     <row r="362">
       <c r="B362" s="3" t="inlineStr">
         <is>
-          <t>helps us keep the cage smelling not as bad</t>
+          <t>she always smells better the day after we put it in</t>
         </is>
       </c>
       <c r="C362" s="4" t="inlineStr">
         <is>
-          <t>JFWOD</t>
+          <t>Hamiledyi</t>
         </is>
       </c>
       <c r="D362" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="E362" s="5">
+        <f>SUM(D362:D362)</f>
+        <v/>
       </c>
     </row>
     <row r="363">
       <c r="B363" s="7" t="inlineStr">
         <is>
-          <t>it neutralizes odor so well</t>
+          <t>Has no smell but did well concealing the odor</t>
         </is>
       </c>
       <c r="C363" s="8" t="inlineStr">
         <is>
-          <t>DR_DUDU</t>
+          <t>Sukh</t>
         </is>
       </c>
       <c r="D363" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E363" s="5">
         <f>SUM(D363:D363)</f>
@@ -6395,33 +6411,42 @@
       </c>
     </row>
     <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>Pleasant Scent</t>
+        </is>
+      </c>
       <c r="B364" s="3" t="inlineStr">
         <is>
-          <t>it neutralizes odor so well</t>
+          <t>smells good</t>
         </is>
       </c>
       <c r="C364" s="4" t="inlineStr">
         <is>
-          <t>Fufuzoie</t>
+          <t>BUCATSTATE</t>
         </is>
       </c>
       <c r="D364" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E364" s="5">
-        <f>SUM(D364:D366)</f>
+        <f>SUM(D364:D372)</f>
+        <v/>
+      </c>
+      <c r="F364" s="6">
+        <f>SUM(E364:E376)</f>
         <v/>
       </c>
     </row>
     <row r="365">
       <c r="B365" s="3" t="inlineStr">
         <is>
-          <t>air within our hamsters habitat stays fresher a bit longer</t>
+          <t>smells natural</t>
         </is>
       </c>
       <c r="C365" s="4" t="inlineStr">
         <is>
-          <t>Fufuzoie</t>
+          <t>BUCATSTATE</t>
         </is>
       </c>
       <c r="D365" s="4" t="n">
@@ -6431,12 +6456,12 @@
     <row r="366">
       <c r="B366" s="3" t="inlineStr">
         <is>
-          <t>help keep the cage fresher between cleanings</t>
+          <t>the petals help give it a nice clean smell</t>
         </is>
       </c>
       <c r="C366" s="4" t="inlineStr">
         <is>
-          <t>Fufuzoie</t>
+          <t>BUCATSTATE</t>
         </is>
       </c>
       <c r="D366" s="4" t="n">
@@ -6444,71 +6469,54 @@
       </c>
     </row>
     <row r="367">
-      <c r="B367" s="7" t="inlineStr">
-        <is>
-          <t>it neutralizes odor so well</t>
-        </is>
-      </c>
-      <c r="C367" s="8" t="inlineStr">
-        <is>
-          <t>Meow&amp;Woof</t>
-        </is>
-      </c>
-      <c r="D367" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E367" s="5">
-        <f>SUM(D367:D367)</f>
-        <v/>
+      <c r="B367" s="3" t="inlineStr">
+        <is>
+          <t>It smells absolutely amazing with the flowers in it as well</t>
+        </is>
+      </c>
+      <c r="C367" s="4" t="inlineStr">
+        <is>
+          <t>BUCATSTATE</t>
+        </is>
+      </c>
+      <c r="D367" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="368">
       <c r="B368" s="3" t="inlineStr">
         <is>
-          <t>she always smells better the day after we put it in</t>
+          <t>It has a nice scent when pouring for the first time</t>
         </is>
       </c>
       <c r="C368" s="4" t="inlineStr">
         <is>
-          <t>Hamiledyi</t>
+          <t>BUCATSTATE</t>
         </is>
       </c>
       <c r="D368" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E368" s="5">
-        <f>SUM(D368:D368)</f>
-        <v/>
-      </c>
     </row>
     <row r="369">
-      <c r="B369" s="7" t="inlineStr">
-        <is>
-          <t>Has no smell but did well concealing the odor</t>
-        </is>
-      </c>
-      <c r="C369" s="8" t="inlineStr">
-        <is>
-          <t>Sukh</t>
-        </is>
-      </c>
-      <c r="D369" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E369" s="5">
-        <f>SUM(D369:D369)</f>
-        <v/>
+      <c r="B369" s="3" t="inlineStr">
+        <is>
+          <t>Clean, low dust, appealing scent</t>
+        </is>
+      </c>
+      <c r="C369" s="4" t="inlineStr">
+        <is>
+          <t>BUCATSTATE</t>
+        </is>
+      </c>
+      <c r="D369" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="2" t="inlineStr">
-        <is>
-          <t>Pleasant Scent</t>
-        </is>
-      </c>
       <c r="B370" s="3" t="inlineStr">
         <is>
-          <t>smells good</t>
+          <t>The scent isn't too overwhelming</t>
         </is>
       </c>
       <c r="C370" s="4" t="inlineStr">
@@ -6517,21 +6525,13 @@
         </is>
       </c>
       <c r="D370" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E370" s="5">
-        <f>SUM(D370:D378)</f>
-        <v/>
-      </c>
-      <c r="F370" s="6">
-        <f>SUM(E370:E382)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="371">
       <c r="B371" s="3" t="inlineStr">
         <is>
-          <t>smells natural</t>
+          <t>It's fresh smelling and very smooth</t>
         </is>
       </c>
       <c r="C371" s="4" t="inlineStr">
@@ -6546,7 +6546,7 @@
     <row r="372">
       <c r="B372" s="3" t="inlineStr">
         <is>
-          <t>the petals help give it a nice clean smell</t>
+          <t>It doesn't stay on hamster but leave a fresh smell on her</t>
         </is>
       </c>
       <c r="C372" s="4" t="inlineStr">
@@ -6559,59 +6559,67 @@
       </c>
     </row>
     <row r="373">
-      <c r="B373" s="3" t="inlineStr">
-        <is>
-          <t>It smells absolutely amazing with the flowers in it as well</t>
-        </is>
-      </c>
-      <c r="C373" s="4" t="inlineStr">
-        <is>
-          <t>BUCATSTATE</t>
-        </is>
-      </c>
-      <c r="D373" s="4" t="n">
-        <v>1</v>
+      <c r="B373" s="7" t="inlineStr">
+        <is>
+          <t>smells good</t>
+        </is>
+      </c>
+      <c r="C373" s="8" t="inlineStr">
+        <is>
+          <t>DR_DUDU</t>
+        </is>
+      </c>
+      <c r="D373" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E373" s="5">
+        <f>SUM(D373:D374)</f>
+        <v/>
       </c>
     </row>
     <row r="374">
-      <c r="B374" s="3" t="inlineStr">
-        <is>
-          <t>It has a nice scent when pouring for the first time</t>
-        </is>
-      </c>
-      <c r="C374" s="4" t="inlineStr">
-        <is>
-          <t>BUCATSTATE</t>
-        </is>
-      </c>
-      <c r="D374" s="4" t="n">
+      <c r="B374" s="7" t="inlineStr">
+        <is>
+          <t>The smell of the flowers is also nice</t>
+        </is>
+      </c>
+      <c r="C374" s="8" t="inlineStr">
+        <is>
+          <t>DR_DUDU</t>
+        </is>
+      </c>
+      <c r="D374" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="375">
       <c r="B375" s="3" t="inlineStr">
         <is>
-          <t>Clean, low dust, appealing scent</t>
+          <t>smells natural</t>
         </is>
       </c>
       <c r="C375" s="4" t="inlineStr">
         <is>
-          <t>BUCATSTATE</t>
+          <t>Fufuzoie</t>
         </is>
       </c>
       <c r="D375" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="E375" s="5">
+        <f>SUM(D375:D376)</f>
+        <v/>
       </c>
     </row>
     <row r="376">
       <c r="B376" s="3" t="inlineStr">
         <is>
-          <t>The scent isn't too overwhelming</t>
+          <t>scented, which I prefer.</t>
         </is>
       </c>
       <c r="C376" s="4" t="inlineStr">
         <is>
-          <t>BUCATSTATE</t>
+          <t>Fufuzoie</t>
         </is>
       </c>
       <c r="D376" s="4" t="n">
@@ -6619,81 +6627,90 @@
       </c>
     </row>
     <row r="377">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>Grooming &amp; Fur Health</t>
+        </is>
+      </c>
       <c r="B377" s="3" t="inlineStr">
         <is>
-          <t>It's fresh smelling and very smooth</t>
+          <t>does a nice job keeping their fur clean and dry</t>
         </is>
       </c>
       <c r="C377" s="4" t="inlineStr">
         <is>
-          <t>BUCATSTATE</t>
+          <t>Fufuzoie</t>
         </is>
       </c>
       <c r="D377" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="E377" s="5">
+        <f>SUM(D377:D380)</f>
+        <v/>
+      </c>
+      <c r="F377" s="6">
+        <f>SUM(E377:E387)</f>
+        <v/>
       </c>
     </row>
     <row r="378">
       <c r="B378" s="3" t="inlineStr">
         <is>
-          <t>It doesn't stay on hamster but leave a fresh smell on her</t>
+          <t>great for removing debris from his fur and paws</t>
         </is>
       </c>
       <c r="C378" s="4" t="inlineStr">
         <is>
+          <t>Fufuzoie</t>
+        </is>
+      </c>
+      <c r="D378" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="B379" s="3" t="inlineStr">
+        <is>
+          <t>used it for grooming without any irritation</t>
+        </is>
+      </c>
+      <c r="C379" s="4" t="inlineStr">
+        <is>
+          <t>Fufuzoie</t>
+        </is>
+      </c>
+      <c r="D379" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="B380" s="3" t="inlineStr">
+        <is>
+          <t>My hamster took to it immediately, rolling around to remove excess oils, leaving his coat looking healthier</t>
+        </is>
+      </c>
+      <c r="C380" s="4" t="inlineStr">
+        <is>
+          <t>Fufuzoie</t>
+        </is>
+      </c>
+      <c r="D380" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="B381" s="7" t="inlineStr">
+        <is>
+          <t>her fur always appears fastidiously groomed and fluffy</t>
+        </is>
+      </c>
+      <c r="C381" s="8" t="inlineStr">
+        <is>
           <t>BUCATSTATE</t>
         </is>
       </c>
-      <c r="D378" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="379">
-      <c r="B379" s="7" t="inlineStr">
-        <is>
-          <t>smells good</t>
-        </is>
-      </c>
-      <c r="C379" s="8" t="inlineStr">
-        <is>
-          <t>DR_DUDU</t>
-        </is>
-      </c>
-      <c r="D379" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E379" s="5">
-        <f>SUM(D379:D380)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="380">
-      <c r="B380" s="7" t="inlineStr">
-        <is>
-          <t>The smell of the flowers is also nice</t>
-        </is>
-      </c>
-      <c r="C380" s="8" t="inlineStr">
-        <is>
-          <t>DR_DUDU</t>
-        </is>
-      </c>
-      <c r="D380" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="381">
-      <c r="B381" s="3" t="inlineStr">
-        <is>
-          <t>smells natural</t>
-        </is>
-      </c>
-      <c r="C381" s="4" t="inlineStr">
-        <is>
-          <t>Fufuzoie</t>
-        </is>
-      </c>
-      <c r="D381" s="4" t="n">
+      <c r="D381" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E381" s="5">
@@ -6702,26 +6719,21 @@
       </c>
     </row>
     <row r="382">
-      <c r="B382" s="3" t="inlineStr">
-        <is>
-          <t>scented, which I prefer.</t>
-        </is>
-      </c>
-      <c r="C382" s="4" t="inlineStr">
-        <is>
-          <t>Fufuzoie</t>
-        </is>
-      </c>
-      <c r="D382" s="4" t="n">
+      <c r="B382" s="7" t="inlineStr">
+        <is>
+          <t>makes it a lot easier for us to groom him</t>
+        </is>
+      </c>
+      <c r="C382" s="8" t="inlineStr">
+        <is>
+          <t>BUCATSTATE</t>
+        </is>
+      </c>
+      <c r="D382" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="2" t="inlineStr">
-        <is>
-          <t>Grooming &amp; Fur Health</t>
-        </is>
-      </c>
       <c r="B383" s="3" t="inlineStr">
         <is>
           <t>does a nice job keeping their fur clean and dry</t>
@@ -6729,30 +6741,26 @@
       </c>
       <c r="C383" s="4" t="inlineStr">
         <is>
-          <t>Fufuzoie</t>
+          <t>JFWOD</t>
         </is>
       </c>
       <c r="D383" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E383" s="5">
-        <f>SUM(D383:D386)</f>
-        <v/>
-      </c>
-      <c r="F383" s="6">
-        <f>SUM(E383:E393)</f>
+        <f>SUM(D383:D384)</f>
         <v/>
       </c>
     </row>
     <row r="384">
       <c r="B384" s="3" t="inlineStr">
         <is>
-          <t>great for removing debris from his fur and paws</t>
+          <t>his fur did start to look a little greasy until we gave him the sand bath</t>
         </is>
       </c>
       <c r="C384" s="4" t="inlineStr">
         <is>
-          <t>Fufuzoie</t>
+          <t>JFWOD</t>
         </is>
       </c>
       <c r="D384" s="4" t="n">
@@ -6760,97 +6768,114 @@
       </c>
     </row>
     <row r="385">
-      <c r="B385" s="3" t="inlineStr">
-        <is>
-          <t>used it for grooming without any irritation</t>
-        </is>
-      </c>
-      <c r="C385" s="4" t="inlineStr">
-        <is>
-          <t>Fufuzoie</t>
-        </is>
-      </c>
-      <c r="D385" s="4" t="n">
-        <v>1</v>
+      <c r="B385" s="7" t="inlineStr">
+        <is>
+          <t>absorbs oils well, leaving his fur super fluffy</t>
+        </is>
+      </c>
+      <c r="C385" s="8" t="inlineStr">
+        <is>
+          <t>DR_DUDU</t>
+        </is>
+      </c>
+      <c r="D385" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E385" s="5">
+        <f>SUM(D385:D385)</f>
+        <v/>
       </c>
     </row>
     <row r="386">
       <c r="B386" s="3" t="inlineStr">
         <is>
-          <t>My hamster took to it immediately, rolling around to remove excess oils, leaving his coat looking healthier</t>
+          <t>seems to clean her face</t>
         </is>
       </c>
       <c r="C386" s="4" t="inlineStr">
         <is>
-          <t>Fufuzoie</t>
+          <t>Hamiledyi</t>
         </is>
       </c>
       <c r="D386" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="E386" s="5">
+        <f>SUM(D386:D386)</f>
+        <v/>
       </c>
     </row>
     <row r="387">
       <c r="B387" s="7" t="inlineStr">
         <is>
-          <t>her fur always appears fastidiously groomed and fluffy</t>
+          <t>helps with his grooming</t>
         </is>
       </c>
       <c r="C387" s="8" t="inlineStr">
         <is>
+          <t>Meow&amp;Woof</t>
+        </is>
+      </c>
+      <c r="D387" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E387" s="5">
+        <f>SUM(D387:D387)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>Larger Size</t>
+        </is>
+      </c>
+      <c r="B388" s="3" t="inlineStr">
+        <is>
+          <t>it's a good size</t>
+        </is>
+      </c>
+      <c r="C388" s="4" t="inlineStr">
+        <is>
           <t>BUCATSTATE</t>
         </is>
       </c>
-      <c r="D387" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E387" s="5">
-        <f>SUM(D387:D388)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="388">
-      <c r="B388" s="7" t="inlineStr">
-        <is>
-          <t>makes it a lot easier for us to groom him</t>
-        </is>
-      </c>
-      <c r="C388" s="8" t="inlineStr">
-        <is>
-          <t>BUCATSTATE</t>
-        </is>
-      </c>
-      <c r="D388" s="8" t="n">
-        <v>1</v>
+      <c r="D388" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E388" s="5">
+        <f>SUM(D388:D390)</f>
+        <v/>
+      </c>
+      <c r="F388" s="6">
+        <f>SUM(E388:E396)</f>
+        <v/>
       </c>
     </row>
     <row r="389">
       <c r="B389" s="3" t="inlineStr">
         <is>
-          <t>does a nice job keeping their fur clean and dry</t>
+          <t>The sand fills the sand bath so it's a good size at about 6lbs in the bag</t>
         </is>
       </c>
       <c r="C389" s="4" t="inlineStr">
         <is>
-          <t>JFWOD</t>
+          <t>BUCATSTATE</t>
         </is>
       </c>
       <c r="D389" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="E389" s="5">
-        <f>SUM(D389:D390)</f>
-        <v/>
       </c>
     </row>
     <row r="390">
       <c r="B390" s="3" t="inlineStr">
         <is>
-          <t>his fur did start to look a little greasy until we gave him the sand bath</t>
+          <t>6.6lbs is a great amount to use for months</t>
         </is>
       </c>
       <c r="C390" s="4" t="inlineStr">
         <is>
-          <t>JFWOD</t>
+          <t>BUCATSTATE</t>
         </is>
       </c>
       <c r="D390" s="4" t="n">
@@ -6860,280 +6885,271 @@
     <row r="391">
       <c r="B391" s="7" t="inlineStr">
         <is>
-          <t>absorbs oils well, leaving his fur super fluffy</t>
+          <t>it's a good size</t>
         </is>
       </c>
       <c r="C391" s="8" t="inlineStr">
         <is>
-          <t>DR_DUDU</t>
+          <t>JFWOD</t>
         </is>
       </c>
       <c r="D391" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E391" s="5">
-        <f>SUM(D391:D391)</f>
+        <f>SUM(D391:D392)</f>
         <v/>
       </c>
     </row>
     <row r="392">
-      <c r="B392" s="3" t="inlineStr">
-        <is>
-          <t>seems to clean her face</t>
-        </is>
-      </c>
-      <c r="C392" s="4" t="inlineStr">
-        <is>
-          <t>Hamiledyi</t>
-        </is>
-      </c>
-      <c r="D392" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E392" s="5">
-        <f>SUM(D392:D392)</f>
-        <v/>
+      <c r="B392" s="7" t="inlineStr">
+        <is>
+          <t>It's a lot of sand and it should last me a good while</t>
+        </is>
+      </c>
+      <c r="C392" s="8" t="inlineStr">
+        <is>
+          <t>JFWOD</t>
+        </is>
+      </c>
+      <c r="D392" s="8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="393">
-      <c r="B393" s="7" t="inlineStr">
-        <is>
-          <t>helps with his grooming</t>
-        </is>
-      </c>
-      <c r="C393" s="8" t="inlineStr">
-        <is>
-          <t>Meow&amp;Woof</t>
-        </is>
-      </c>
-      <c r="D393" s="8" t="n">
+      <c r="B393" s="3" t="inlineStr">
+        <is>
+          <t>it's a good size</t>
+        </is>
+      </c>
+      <c r="C393" s="4" t="inlineStr">
+        <is>
+          <t>Sukh</t>
+        </is>
+      </c>
+      <c r="D393" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E393" s="5">
-        <f>SUM(D393:D393)</f>
+        <f>SUM(D393:D394)</f>
         <v/>
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="2" t="inlineStr">
-        <is>
-          <t>Larger Size</t>
-        </is>
-      </c>
       <c r="B394" s="3" t="inlineStr">
         <is>
-          <t>it's a good size</t>
+          <t>size it perfect</t>
         </is>
       </c>
       <c r="C394" s="4" t="inlineStr">
         <is>
-          <t>BUCATSTATE</t>
+          <t>Sukh</t>
         </is>
       </c>
       <c r="D394" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E394" s="5">
-        <f>SUM(D394:D396)</f>
-        <v/>
-      </c>
-      <c r="F394" s="6">
-        <f>SUM(E394:E402)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="395">
-      <c r="B395" s="3" t="inlineStr">
-        <is>
-          <t>The sand fills the sand bath so it's a good size at about 6lbs in the bag</t>
-        </is>
-      </c>
-      <c r="C395" s="4" t="inlineStr">
-        <is>
-          <t>BUCATSTATE</t>
-        </is>
-      </c>
-      <c r="D395" s="4" t="n">
-        <v>1</v>
+      <c r="B395" s="7" t="inlineStr">
+        <is>
+          <t>perfect size for my dwarf hamster</t>
+        </is>
+      </c>
+      <c r="C395" s="8" t="inlineStr">
+        <is>
+          <t>DR_DUDU</t>
+        </is>
+      </c>
+      <c r="D395" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E395" s="5">
+        <f>SUM(D395:D395)</f>
+        <v/>
       </c>
     </row>
     <row r="396">
       <c r="B396" s="3" t="inlineStr">
         <is>
-          <t>6.6lbs is a great amount to use for months</t>
+          <t>The 15oz size is convenient and lasts a decent amount of time</t>
         </is>
       </c>
       <c r="C396" s="4" t="inlineStr">
         <is>
+          <t>Fufuzoie</t>
+        </is>
+      </c>
+      <c r="D396" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E396" s="5">
+        <f>SUM(D396:D396)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="inlineStr">
+        <is>
+          <t>Litter Box / Potty Use</t>
+        </is>
+      </c>
+      <c r="B397" s="3" t="inlineStr">
+        <is>
+          <t>It's definitely helped confine his bathroom area and helps keep the rest of his cage clean</t>
+        </is>
+      </c>
+      <c r="C397" s="4" t="inlineStr">
+        <is>
           <t>BUCATSTATE</t>
         </is>
       </c>
-      <c r="D396" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="397">
-      <c r="B397" s="7" t="inlineStr">
-        <is>
-          <t>it's a good size</t>
-        </is>
-      </c>
-      <c r="C397" s="8" t="inlineStr">
-        <is>
-          <t>JFWOD</t>
-        </is>
-      </c>
-      <c r="D397" s="8" t="n">
-        <v>2</v>
+      <c r="D397" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="E397" s="5">
         <f>SUM(D397:D398)</f>
         <v/>
       </c>
+      <c r="F397" s="6">
+        <f>SUM(E397:E405)</f>
+        <v/>
+      </c>
     </row>
     <row r="398">
-      <c r="B398" s="7" t="inlineStr">
-        <is>
-          <t>It's a lot of sand and it should last me a good while</t>
-        </is>
-      </c>
-      <c r="C398" s="8" t="inlineStr">
-        <is>
-          <t>JFWOD</t>
-        </is>
-      </c>
-      <c r="D398" s="8" t="n">
+      <c r="B398" s="3" t="inlineStr">
+        <is>
+          <t>easier for me to clean up and less stinky than him peeing in his bedding</t>
+        </is>
+      </c>
+      <c r="C398" s="4" t="inlineStr">
+        <is>
+          <t>BUCATSTATE</t>
+        </is>
+      </c>
+      <c r="D398" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="399">
-      <c r="B399" s="3" t="inlineStr">
-        <is>
-          <t>it's a good size</t>
-        </is>
-      </c>
-      <c r="C399" s="4" t="inlineStr">
-        <is>
-          <t>Sukh</t>
-        </is>
-      </c>
-      <c r="D399" s="4" t="n">
-        <v>1</v>
+      <c r="B399" s="7" t="inlineStr">
+        <is>
+          <t>It's definitely helped confine his bathroom area and helps keep the rest of his cage clean</t>
+        </is>
+      </c>
+      <c r="C399" s="8" t="inlineStr">
+        <is>
+          <t>Hamiledyi</t>
+        </is>
+      </c>
+      <c r="D399" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="E399" s="5">
-        <f>SUM(D399:D400)</f>
+        <f>SUM(D399:D399)</f>
         <v/>
       </c>
     </row>
     <row r="400">
       <c r="B400" s="3" t="inlineStr">
         <is>
-          <t>size it perfect</t>
+          <t>It's definitely helped confine his bathroom area and helps keep the rest of his cage clean</t>
         </is>
       </c>
       <c r="C400" s="4" t="inlineStr">
         <is>
-          <t>Sukh</t>
+          <t>DR_DUDU</t>
         </is>
       </c>
       <c r="D400" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="E400" s="5">
+        <f>SUM(D400:D401)</f>
+        <v/>
+      </c>
     </row>
     <row r="401">
-      <c r="B401" s="7" t="inlineStr">
-        <is>
-          <t>perfect size for my dwarf hamster</t>
-        </is>
-      </c>
-      <c r="C401" s="8" t="inlineStr">
-        <is>
-          <t>DR_DUDU</t>
-        </is>
-      </c>
-      <c r="D401" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E401" s="5">
-        <f>SUM(D401:D401)</f>
-        <v/>
+      <c r="B401" s="3" t="inlineStr">
+        <is>
+          <t>My hamsters are happy getting their latrine cleaned with the new sand</t>
+        </is>
+      </c>
+      <c r="C401" s="4" t="inlineStr">
+        <is>
+          <t>DR_DUDU</t>
+        </is>
+      </c>
+      <c r="D401" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="402">
-      <c r="B402" s="3" t="inlineStr">
-        <is>
-          <t>The 15oz size is convenient and lasts a decent amount of time</t>
-        </is>
-      </c>
-      <c r="C402" s="4" t="inlineStr">
-        <is>
-          <t>Fufuzoie</t>
-        </is>
-      </c>
-      <c r="D402" s="4" t="n">
+      <c r="B402" s="7" t="inlineStr">
+        <is>
+          <t>Easy for them to use to go potty too</t>
+        </is>
+      </c>
+      <c r="C402" s="8" t="inlineStr">
+        <is>
+          <t>JFWOD</t>
+        </is>
+      </c>
+      <c r="D402" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E402" s="5">
-        <f>SUM(D402:D402)</f>
+        <f>SUM(D402:D403)</f>
         <v/>
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="2" t="inlineStr">
-        <is>
-          <t>Litter Box / Potty Use</t>
-        </is>
-      </c>
-      <c r="B403" s="3" t="inlineStr">
-        <is>
-          <t>It's definitely helped confine his bathroom area and helps keep the rest of his cage clean</t>
-        </is>
-      </c>
-      <c r="C403" s="4" t="inlineStr">
-        <is>
-          <t>BUCATSTATE</t>
-        </is>
-      </c>
-      <c r="D403" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E403" s="5">
-        <f>SUM(D403:D404)</f>
-        <v/>
-      </c>
-      <c r="F403" s="6">
-        <f>SUM(E403:E411)</f>
-        <v/>
+      <c r="B403" s="7" t="inlineStr">
+        <is>
+          <t>It's like potty training!(urine only)</t>
+        </is>
+      </c>
+      <c r="C403" s="8" t="inlineStr">
+        <is>
+          <t>JFWOD</t>
+        </is>
+      </c>
+      <c r="D403" s="8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="404">
       <c r="B404" s="3" t="inlineStr">
         <is>
-          <t>easier for me to clean up and less stinky than him peeing in his bedding</t>
+          <t>It's definitely helped confine his bathroom area and helps keep the rest of his cage clean</t>
         </is>
       </c>
       <c r="C404" s="4" t="inlineStr">
         <is>
-          <t>BUCATSTATE</t>
+          <t>Meow&amp;Woof</t>
         </is>
       </c>
       <c r="D404" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="E404" s="5">
+        <f>SUM(D404:D404)</f>
+        <v/>
       </c>
     </row>
     <row r="405">
       <c r="B405" s="7" t="inlineStr">
         <is>
-          <t>It's definitely helped confine his bathroom area and helps keep the rest of his cage clean</t>
+          <t>acting as a great natural potty litter</t>
         </is>
       </c>
       <c r="C405" s="8" t="inlineStr">
         <is>
-          <t>Hamiledyi</t>
+          <t>Fufuzoie</t>
         </is>
       </c>
       <c r="D405" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E405" s="5">
         <f>SUM(D405:D405)</f>
@@ -7141,33 +7157,42 @@
       </c>
     </row>
     <row r="406">
+      <c r="A406" s="2" t="inlineStr">
+        <is>
+          <t>Gerbils</t>
+        </is>
+      </c>
       <c r="B406" s="3" t="inlineStr">
         <is>
-          <t>It's definitely helped confine his bathroom area and helps keep the rest of his cage clean</t>
+          <t>My daughter's gerbils love this stuff</t>
         </is>
       </c>
       <c r="C406" s="4" t="inlineStr">
         <is>
-          <t>DR_DUDU</t>
+          <t>JFWOD</t>
         </is>
       </c>
       <c r="D406" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E406" s="5">
         <f>SUM(D406:D407)</f>
         <v/>
       </c>
+      <c r="F406" s="6">
+        <f>SUM(E406:E410)</f>
+        <v/>
+      </c>
     </row>
     <row r="407">
       <c r="B407" s="3" t="inlineStr">
         <is>
-          <t>My hamsters are happy getting their latrine cleaned with the new sand</t>
+          <t>My gerbil jumped and flopped onto his side when i put this sand in his enclosure</t>
         </is>
       </c>
       <c r="C407" s="4" t="inlineStr">
         <is>
-          <t>DR_DUDU</t>
+          <t>JFWOD</t>
         </is>
       </c>
       <c r="D407" s="4" t="n">
@@ -7177,12 +7202,12 @@
     <row r="408">
       <c r="B408" s="7" t="inlineStr">
         <is>
-          <t>Easy for them to use to go potty too</t>
+          <t>My daughter's gerbils love this stuff</t>
         </is>
       </c>
       <c r="C408" s="8" t="inlineStr">
         <is>
-          <t>JFWOD</t>
+          <t>DR_DUDU</t>
         </is>
       </c>
       <c r="D408" s="8" t="n">
@@ -7196,12 +7221,12 @@
     <row r="409">
       <c r="B409" s="7" t="inlineStr">
         <is>
-          <t>It's like potty training!(urine only)</t>
+          <t>My gerbil has no hesitation using the sand.</t>
         </is>
       </c>
       <c r="C409" s="8" t="inlineStr">
         <is>
-          <t>JFWOD</t>
+          <t>DR_DUDU</t>
         </is>
       </c>
       <c r="D409" s="8" t="n">
@@ -7211,16 +7236,16 @@
     <row r="410">
       <c r="B410" s="3" t="inlineStr">
         <is>
-          <t>It's definitely helped confine his bathroom area and helps keep the rest of his cage clean</t>
+          <t>My daughter's gerbils love this stuff</t>
         </is>
       </c>
       <c r="C410" s="4" t="inlineStr">
         <is>
-          <t>Meow&amp;Woof</t>
+          <t>BUCATSTATE</t>
         </is>
       </c>
       <c r="D410" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E410" s="5">
         <f>SUM(D410:D410)</f>
@@ -7228,56 +7253,56 @@
       </c>
     </row>
     <row r="411">
-      <c r="B411" s="7" t="inlineStr">
-        <is>
-          <t>acting as a great natural potty litter</t>
-        </is>
-      </c>
-      <c r="C411" s="8" t="inlineStr">
-        <is>
-          <t>Fufuzoie</t>
-        </is>
-      </c>
-      <c r="D411" s="8" t="n">
-        <v>1</v>
+      <c r="A411" s="2" t="inlineStr">
+        <is>
+          <t>Natural &amp; Non-Toxic</t>
+        </is>
+      </c>
+      <c r="B411" s="3" t="inlineStr">
+        <is>
+          <t>Nothing wrong with our hamster for using a few months</t>
+        </is>
+      </c>
+      <c r="C411" s="4" t="inlineStr">
+        <is>
+          <t>Hamiledyi</t>
+        </is>
+      </c>
+      <c r="D411" s="4" t="n">
+        <v>3</v>
       </c>
       <c r="E411" s="5">
         <f>SUM(D411:D411)</f>
         <v/>
       </c>
+      <c r="F411" s="6">
+        <f>SUM(E411:E415)</f>
+        <v/>
+      </c>
     </row>
     <row r="412">
-      <c r="A412" s="2" t="inlineStr">
-        <is>
-          <t>Gerbils</t>
-        </is>
-      </c>
-      <c r="B412" s="3" t="inlineStr">
-        <is>
-          <t>My daughter's gerbils love this stuff</t>
-        </is>
-      </c>
-      <c r="C412" s="4" t="inlineStr">
-        <is>
-          <t>JFWOD</t>
-        </is>
-      </c>
-      <c r="D412" s="4" t="n">
-        <v>3</v>
+      <c r="B412" s="7" t="inlineStr">
+        <is>
+          <t>Nothing wrong with our hamster for using a few months</t>
+        </is>
+      </c>
+      <c r="C412" s="8" t="inlineStr">
+        <is>
+          <t>DR_DUDU</t>
+        </is>
+      </c>
+      <c r="D412" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="E412" s="5">
-        <f>SUM(D412:D413)</f>
-        <v/>
-      </c>
-      <c r="F412" s="6">
-        <f>SUM(E412:E416)</f>
+        <f>SUM(D412:D412)</f>
         <v/>
       </c>
     </row>
     <row r="413">
       <c r="B413" s="3" t="inlineStr">
         <is>
-          <t>My gerbil jumped and flopped onto his side when i put this sand in his enclosure</t>
+          <t>Nothing wrong with our hamster for using a few months</t>
         </is>
       </c>
       <c r="C413" s="4" t="inlineStr">
@@ -7287,93 +7312,97 @@
       </c>
       <c r="D413" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="E413" s="5">
+        <f>SUM(D413:D413)</f>
+        <v/>
       </c>
     </row>
     <row r="414">
       <c r="B414" s="7" t="inlineStr">
         <is>
-          <t>My daughter's gerbils love this stuff</t>
+          <t>Nothing wrong with our hamster for using a few months</t>
         </is>
       </c>
       <c r="C414" s="8" t="inlineStr">
         <is>
-          <t>DR_DUDU</t>
+          <t>Fufuzoie</t>
         </is>
       </c>
       <c r="D414" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E414" s="5">
-        <f>SUM(D414:D415)</f>
+        <f>SUM(D414:D414)</f>
         <v/>
       </c>
     </row>
     <row r="415">
-      <c r="B415" s="7" t="inlineStr">
-        <is>
-          <t>My gerbil has no hesitation using the sand.</t>
-        </is>
-      </c>
-      <c r="C415" s="8" t="inlineStr">
-        <is>
-          <t>DR_DUDU</t>
-        </is>
-      </c>
-      <c r="D415" s="8" t="n">
-        <v>1</v>
+      <c r="B415" s="3" t="inlineStr">
+        <is>
+          <t>Nothing wrong with our hamster for using a few months</t>
+        </is>
+      </c>
+      <c r="C415" s="4" t="inlineStr">
+        <is>
+          <t>Sukh</t>
+        </is>
+      </c>
+      <c r="D415" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E415" s="5">
+        <f>SUM(D415:D415)</f>
+        <v/>
       </c>
     </row>
     <row r="416">
+      <c r="A416" s="2" t="inlineStr">
+        <is>
+          <t>Resealable/Airtight Packaging</t>
+        </is>
+      </c>
       <c r="B416" s="3" t="inlineStr">
         <is>
-          <t>My daughter's gerbils love this stuff</t>
+          <t>It's easily resealable for future uses</t>
         </is>
       </c>
       <c r="C416" s="4" t="inlineStr">
         <is>
-          <t>BUCATSTATE</t>
+          <t>Fufuzoie</t>
         </is>
       </c>
       <c r="D416" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E416" s="5">
-        <f>SUM(D416:D416)</f>
+        <f>SUM(D416:D417)</f>
+        <v/>
+      </c>
+      <c r="F416" s="6">
+        <f>SUM(E416:E420)</f>
         <v/>
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="2" t="inlineStr">
-        <is>
-          <t>Natural &amp; Non-Toxic</t>
-        </is>
-      </c>
       <c r="B417" s="3" t="inlineStr">
         <is>
-          <t>Nothing wrong with our hamster for using a few months</t>
+          <t>The resealable closure keeps the rest fresh and dry between uses</t>
         </is>
       </c>
       <c r="C417" s="4" t="inlineStr">
         <is>
-          <t>Hamiledyi</t>
+          <t>Fufuzoie</t>
         </is>
       </c>
       <c r="D417" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E417" s="5">
-        <f>SUM(D417:D417)</f>
-        <v/>
-      </c>
-      <c r="F417" s="6">
-        <f>SUM(E417:E421)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="418">
       <c r="B418" s="7" t="inlineStr">
         <is>
-          <t>Nothing wrong with our hamster for using a few months</t>
+          <t>It's easily resealable for future uses</t>
         </is>
       </c>
       <c r="C418" s="8" t="inlineStr">
@@ -7392,7 +7421,7 @@
     <row r="419">
       <c r="B419" s="3" t="inlineStr">
         <is>
-          <t>Nothing wrong with our hamster for using a few months</t>
+          <t>It's easily resealable for future uses</t>
         </is>
       </c>
       <c r="C419" s="4" t="inlineStr">
@@ -7411,12 +7440,12 @@
     <row r="420">
       <c r="B420" s="7" t="inlineStr">
         <is>
-          <t>Nothing wrong with our hamster for using a few months</t>
+          <t>It's easily resealable for future uses</t>
         </is>
       </c>
       <c r="C420" s="8" t="inlineStr">
         <is>
-          <t>Fufuzoie</t>
+          <t>BUCATSTATE</t>
         </is>
       </c>
       <c r="D420" s="8" t="n">
@@ -7428,71 +7457,67 @@
       </c>
     </row>
     <row r="421">
+      <c r="A421" s="2" t="inlineStr">
+        <is>
+          <t>Good for Health</t>
+        </is>
+      </c>
       <c r="B421" s="3" t="inlineStr">
         <is>
-          <t>Nothing wrong with our hamster for using a few months</t>
+          <t>great for her health</t>
         </is>
       </c>
       <c r="C421" s="4" t="inlineStr">
         <is>
-          <t>Sukh</t>
+          <t>JFWOD</t>
         </is>
       </c>
       <c r="D421" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E421" s="5">
-        <f>SUM(D421:D421)</f>
+        <f>SUM(D421:D423)</f>
+        <v/>
+      </c>
+      <c r="F421" s="6">
+        <f>SUM(E421:E426)</f>
         <v/>
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="2" t="inlineStr">
-        <is>
-          <t>Resealable/Airtight Packaging</t>
-        </is>
-      </c>
       <c r="B422" s="3" t="inlineStr">
         <is>
-          <t>It's easily resealable for future uses</t>
+          <t>Healthy for my hammies to clean themselves</t>
         </is>
       </c>
       <c r="C422" s="4" t="inlineStr">
         <is>
-          <t>Fufuzoie</t>
+          <t>JFWOD</t>
         </is>
       </c>
       <c r="D422" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E422" s="5">
-        <f>SUM(D422:D423)</f>
-        <v/>
-      </c>
-      <c r="F422" s="6">
-        <f>SUM(E422:E426)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="423">
       <c r="B423" s="3" t="inlineStr">
         <is>
-          <t>The resealable closure keeps the rest fresh and dry between uses</t>
+          <t>my quail are content and laying a plentiful supply of eggs</t>
         </is>
       </c>
       <c r="C423" s="4" t="inlineStr">
         <is>
-          <t>Fufuzoie</t>
+          <t>JFWOD</t>
         </is>
       </c>
       <c r="D423" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="424">
       <c r="B424" s="7" t="inlineStr">
         <is>
-          <t>It's easily resealable for future uses</t>
+          <t>I can tell if she's dehydrated when she pees in it.</t>
         </is>
       </c>
       <c r="C424" s="8" t="inlineStr">
@@ -7501,44 +7526,40 @@
         </is>
       </c>
       <c r="D424" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E424" s="5">
-        <f>SUM(D424:D424)</f>
+        <f>SUM(D424:D425)</f>
         <v/>
       </c>
     </row>
     <row r="425">
-      <c r="B425" s="3" t="inlineStr">
-        <is>
-          <t>It's easily resealable for future uses</t>
-        </is>
-      </c>
-      <c r="C425" s="4" t="inlineStr">
-        <is>
-          <t>JFWOD</t>
-        </is>
-      </c>
-      <c r="D425" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E425" s="5">
-        <f>SUM(D425:D425)</f>
-        <v/>
+      <c r="B425" s="7" t="inlineStr">
+        <is>
+          <t>great for her health</t>
+        </is>
+      </c>
+      <c r="C425" s="8" t="inlineStr">
+        <is>
+          <t>DR_DUDU</t>
+        </is>
+      </c>
+      <c r="D425" s="8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="426">
-      <c r="B426" s="7" t="inlineStr">
-        <is>
-          <t>It's easily resealable for future uses</t>
-        </is>
-      </c>
-      <c r="C426" s="8" t="inlineStr">
-        <is>
-          <t>BUCATSTATE</t>
-        </is>
-      </c>
-      <c r="D426" s="8" t="n">
+      <c r="B426" s="3" t="inlineStr">
+        <is>
+          <t>seems to help them with itching</t>
+        </is>
+      </c>
+      <c r="C426" s="4" t="inlineStr">
+        <is>
+          <t>Fufuzoie</t>
+        </is>
+      </c>
+      <c r="D426" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E426" s="5">
@@ -7549,40 +7570,40 @@
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>Good for Health</t>
+          <t>Handy Scooper</t>
         </is>
       </c>
       <c r="B427" s="3" t="inlineStr">
         <is>
-          <t>great for her health</t>
+          <t>the little scooper is handy</t>
         </is>
       </c>
       <c r="C427" s="4" t="inlineStr">
         <is>
-          <t>JFWOD</t>
+          <t>BUCATSTATE</t>
         </is>
       </c>
       <c r="D427" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E427" s="5">
-        <f>SUM(D427:D429)</f>
+        <f>SUM(D427:D428)</f>
         <v/>
       </c>
       <c r="F427" s="6">
-        <f>SUM(E427:E432)</f>
+        <f>SUM(E427:E428)</f>
         <v/>
       </c>
     </row>
     <row r="428">
       <c r="B428" s="3" t="inlineStr">
         <is>
-          <t>Healthy for my hammies to clean themselves</t>
+          <t>it does make noticeable clumps that can be scooped out with the included scooper</t>
         </is>
       </c>
       <c r="C428" s="4" t="inlineStr">
         <is>
-          <t>JFWOD</t>
+          <t>BUCATSTATE</t>
         </is>
       </c>
       <c r="D428" s="4" t="n">
@@ -7590,66 +7611,83 @@
       </c>
     </row>
     <row r="429">
+      <c r="A429" s="2" t="inlineStr">
+        <is>
+          <t>Absorbs Urine Well</t>
+        </is>
+      </c>
       <c r="B429" s="3" t="inlineStr">
         <is>
-          <t>my quail are content and laying a plentiful supply of eggs</t>
+          <t>Absorbs wonderfully</t>
         </is>
       </c>
       <c r="C429" s="4" t="inlineStr">
         <is>
-          <t>JFWOD</t>
+          <t>DR_DUDU</t>
         </is>
       </c>
       <c r="D429" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="E429" s="5">
+        <f>SUM(D429:D429)</f>
+        <v/>
+      </c>
+      <c r="F429" s="6">
+        <f>SUM(E429:E432)</f>
+        <v/>
       </c>
     </row>
     <row r="430">
       <c r="B430" s="7" t="inlineStr">
         <is>
-          <t>I can tell if she's dehydrated when she pees in it.</t>
+          <t>Absorbs wonderfully</t>
         </is>
       </c>
       <c r="C430" s="8" t="inlineStr">
         <is>
-          <t>DR_DUDU</t>
+          <t>BUCATSTATE</t>
         </is>
       </c>
       <c r="D430" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E430" s="5">
-        <f>SUM(D430:D431)</f>
+        <f>SUM(D430:D430)</f>
         <v/>
       </c>
     </row>
     <row r="431">
-      <c r="B431" s="7" t="inlineStr">
-        <is>
-          <t>great for her health</t>
-        </is>
-      </c>
-      <c r="C431" s="8" t="inlineStr">
-        <is>
-          <t>DR_DUDU</t>
-        </is>
-      </c>
-      <c r="D431" s="8" t="n">
-        <v>1</v>
+      <c r="B431" s="3" t="inlineStr">
+        <is>
+          <t>Absorbs wonderfully</t>
+        </is>
+      </c>
+      <c r="C431" s="4" t="inlineStr">
+        <is>
+          <t>Meow&amp;Woof</t>
+        </is>
+      </c>
+      <c r="D431" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E431" s="5">
+        <f>SUM(D431:D431)</f>
+        <v/>
       </c>
     </row>
     <row r="432">
-      <c r="B432" s="3" t="inlineStr">
-        <is>
-          <t>seems to help them with itching</t>
-        </is>
-      </c>
-      <c r="C432" s="4" t="inlineStr">
-        <is>
-          <t>Fufuzoie</t>
-        </is>
-      </c>
-      <c r="D432" s="4" t="n">
+      <c r="B432" s="7" t="inlineStr">
+        <is>
+          <t>Absorbs wonderfully</t>
+        </is>
+      </c>
+      <c r="C432" s="8" t="inlineStr">
+        <is>
+          <t>JFWOD</t>
+        </is>
+      </c>
+      <c r="D432" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E432" s="5">
@@ -7660,40 +7698,40 @@
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
         <is>
-          <t>Handy Scooper</t>
+          <t>Better Than Competitors</t>
         </is>
       </c>
       <c r="B433" s="3" t="inlineStr">
         <is>
-          <t>the little scooper is handy</t>
+          <t>Way better and healthier than the Kaytee dust from the pet store</t>
         </is>
       </c>
       <c r="C433" s="4" t="inlineStr">
         <is>
-          <t>BUCATSTATE</t>
+          <t>Hamiledyi</t>
         </is>
       </c>
       <c r="D433" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E433" s="5">
         <f>SUM(D433:D434)</f>
         <v/>
       </c>
       <c r="F433" s="6">
-        <f>SUM(E433:E434)</f>
+        <f>SUM(E433:E438)</f>
         <v/>
       </c>
     </row>
     <row r="434">
       <c r="B434" s="3" t="inlineStr">
         <is>
-          <t>it does make noticeable clumps that can be scooped out with the included scooper</t>
+          <t>This sand is hands down 100% better than any of the dust baths we've tried</t>
         </is>
       </c>
       <c r="C434" s="4" t="inlineStr">
         <is>
-          <t>BUCATSTATE</t>
+          <t>Hamiledyi</t>
         </is>
       </c>
       <c r="D434" s="4" t="n">
@@ -7701,61 +7739,48 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" s="2" t="inlineStr">
-        <is>
-          <t>Absorbs Urine Well</t>
-        </is>
-      </c>
-      <c r="B435" s="3" t="inlineStr">
-        <is>
-          <t>Absorbs wonderfully</t>
-        </is>
-      </c>
-      <c r="C435" s="4" t="inlineStr">
-        <is>
-          <t>DR_DUDU</t>
-        </is>
-      </c>
-      <c r="D435" s="4" t="n">
-        <v>3</v>
+      <c r="B435" s="7" t="inlineStr">
+        <is>
+          <t>This sand is hands down 100% better than any of the dust baths we've tried</t>
+        </is>
+      </c>
+      <c r="C435" s="8" t="inlineStr">
+        <is>
+          <t>JFWOD</t>
+        </is>
+      </c>
+      <c r="D435" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="E435" s="5">
-        <f>SUM(D435:D435)</f>
-        <v/>
-      </c>
-      <c r="F435" s="6">
-        <f>SUM(E435:E438)</f>
+        <f>SUM(D435:D436)</f>
         <v/>
       </c>
     </row>
     <row r="436">
       <c r="B436" s="7" t="inlineStr">
         <is>
-          <t>Absorbs wonderfully</t>
+          <t>like this more than their usual sand</t>
         </is>
       </c>
       <c r="C436" s="8" t="inlineStr">
         <is>
-          <t>BUCATSTATE</t>
+          <t>JFWOD</t>
         </is>
       </c>
       <c r="D436" s="8" t="n">
         <v>1</v>
-      </c>
-      <c r="E436" s="5">
-        <f>SUM(D436:D436)</f>
-        <v/>
       </c>
     </row>
     <row r="437">
       <c r="B437" s="3" t="inlineStr">
         <is>
-          <t>Absorbs wonderfully</t>
+          <t>Now I find this product much better than cat litter</t>
         </is>
       </c>
       <c r="C437" s="4" t="inlineStr">
         <is>
-          <t>Meow&amp;Woof</t>
+          <t>BUCATSTATE</t>
         </is>
       </c>
       <c r="D437" s="4" t="n">
@@ -7769,12 +7794,12 @@
     <row r="438">
       <c r="B438" s="7" t="inlineStr">
         <is>
-          <t>It's good for adsorption</t>
+          <t>this brand of the white does seem to be better than other brands we have tried</t>
         </is>
       </c>
       <c r="C438" s="8" t="inlineStr">
         <is>
-          <t>JFWOD</t>
+          <t>Fufuzoie</t>
         </is>
       </c>
       <c r="D438" s="8" t="n">
@@ -7788,24 +7813,24 @@
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
         <is>
-          <t>Better Than Competitors</t>
+          <t>Loyal Customer</t>
         </is>
       </c>
       <c r="B439" s="3" t="inlineStr">
         <is>
-          <t>Way better and healthier than the Kaytee dust from the pet store</t>
+          <t>I have been using this sand for over 2 years now</t>
         </is>
       </c>
       <c r="C439" s="4" t="inlineStr">
         <is>
-          <t>Hamiledyi</t>
+          <t>JFWOD</t>
         </is>
       </c>
       <c r="D439" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E439" s="5">
-        <f>SUM(D439:D440)</f>
+        <f>SUM(D439:D441)</f>
         <v/>
       </c>
       <c r="F439" s="6">
@@ -7816,12 +7841,12 @@
     <row r="440">
       <c r="B440" s="3" t="inlineStr">
         <is>
-          <t>This sand is hands down 100% better than any of the dust baths we've tried</t>
+          <t>This is my go to sand for my hamsters</t>
         </is>
       </c>
       <c r="C440" s="4" t="inlineStr">
         <is>
-          <t>Hamiledyi</t>
+          <t>JFWOD</t>
         </is>
       </c>
       <c r="D440" s="4" t="n">
@@ -7829,48 +7854,48 @@
       </c>
     </row>
     <row r="441">
-      <c r="B441" s="7" t="inlineStr">
-        <is>
-          <t>This sand is hands down 100% better than any of the dust baths we've tried</t>
-        </is>
-      </c>
-      <c r="C441" s="8" t="inlineStr">
-        <is>
-          <t>JFWOD</t>
-        </is>
-      </c>
-      <c r="D441" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E441" s="5">
-        <f>SUM(D441:D442)</f>
-        <v/>
+      <c r="B441" s="3" t="inlineStr">
+        <is>
+          <t>This is my favorite dust for chinchilla</t>
+        </is>
+      </c>
+      <c r="C441" s="4" t="inlineStr">
+        <is>
+          <t>JFWOD</t>
+        </is>
+      </c>
+      <c r="D441" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="442">
       <c r="B442" s="7" t="inlineStr">
         <is>
-          <t>like this more than their usual sand</t>
+          <t>This is my go to sand for my hamsters</t>
         </is>
       </c>
       <c r="C442" s="8" t="inlineStr">
         <is>
-          <t>JFWOD</t>
+          <t>DR_DUDU</t>
         </is>
       </c>
       <c r="D442" s="8" t="n">
         <v>1</v>
+      </c>
+      <c r="E442" s="5">
+        <f>SUM(D442:D442)</f>
+        <v/>
       </c>
     </row>
     <row r="443">
       <c r="B443" s="3" t="inlineStr">
         <is>
-          <t>Now I find this product much better than cat litter</t>
+          <t>This is my go to sand for my hamsters</t>
         </is>
       </c>
       <c r="C443" s="4" t="inlineStr">
         <is>
-          <t>BUCATSTATE</t>
+          <t>Hamiledyi</t>
         </is>
       </c>
       <c r="D443" s="4" t="n">
@@ -7884,12 +7909,12 @@
     <row r="444">
       <c r="B444" s="7" t="inlineStr">
         <is>
-          <t>this brand of the white does seem to be better than other brands we have tried</t>
+          <t>This is my go to sand for my hamsters</t>
         </is>
       </c>
       <c r="C444" s="8" t="inlineStr">
         <is>
-          <t>Fufuzoie</t>
+          <t>BUCATSTATE</t>
         </is>
       </c>
       <c r="D444" s="8" t="n">
@@ -7903,70 +7928,87 @@
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
         <is>
-          <t>Loyal Customer</t>
+          <t>Cute Flower Petals</t>
         </is>
       </c>
       <c r="B445" s="3" t="inlineStr">
         <is>
-          <t>I have been using this sand for over 2 years now</t>
+          <t>Love the flowers in it</t>
         </is>
       </c>
       <c r="C445" s="4" t="inlineStr">
         <is>
-          <t>JFWOD</t>
+          <t>BUCATSTATE</t>
         </is>
       </c>
       <c r="D445" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E445" s="5">
-        <f>SUM(D445:D447)</f>
+        <f>SUM(D445:D445)</f>
         <v/>
       </c>
       <c r="F445" s="6">
-        <f>SUM(E445:E450)</f>
+        <f>SUM(E445:E446)</f>
         <v/>
       </c>
     </row>
     <row r="446">
-      <c r="B446" s="3" t="inlineStr">
-        <is>
-          <t>This is my go to sand for my hamsters</t>
-        </is>
-      </c>
-      <c r="C446" s="4" t="inlineStr">
-        <is>
-          <t>JFWOD</t>
-        </is>
-      </c>
-      <c r="D446" s="4" t="n">
-        <v>1</v>
+      <c r="B446" s="7" t="inlineStr">
+        <is>
+          <t>The smell of the flowers is also nice</t>
+        </is>
+      </c>
+      <c r="C446" s="8" t="inlineStr">
+        <is>
+          <t>DR_DUDU</t>
+        </is>
+      </c>
+      <c r="D446" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E446" s="5">
+        <f>SUM(D446:D446)</f>
+        <v/>
       </c>
     </row>
     <row r="447">
+      <c r="A447" s="2" t="inlineStr">
+        <is>
+          <t>Craft / Décor Use</t>
+        </is>
+      </c>
       <c r="B447" s="3" t="inlineStr">
         <is>
-          <t>This is my favorite dust for chinchilla</t>
+          <t>best sand for crafts</t>
         </is>
       </c>
       <c r="C447" s="4" t="inlineStr">
         <is>
-          <t>JFWOD</t>
+          <t>DR_DUDU</t>
         </is>
       </c>
       <c r="D447" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="E447" s="5">
+        <f>SUM(D447:D447)</f>
+        <v/>
+      </c>
+      <c r="F447" s="6">
+        <f>SUM(E447:E449)</f>
+        <v/>
       </c>
     </row>
     <row r="448">
       <c r="B448" s="7" t="inlineStr">
         <is>
-          <t>This is my go to sand for my hamsters</t>
+          <t>best sand for crafts</t>
         </is>
       </c>
       <c r="C448" s="8" t="inlineStr">
         <is>
-          <t>DR_DUDU</t>
+          <t>BUCATSTATE</t>
         </is>
       </c>
       <c r="D448" s="8" t="n">
@@ -7980,12 +8022,12 @@
     <row r="449">
       <c r="B449" s="3" t="inlineStr">
         <is>
-          <t>This is my go to sand for my hamsters</t>
+          <t>best sand for crafts</t>
         </is>
       </c>
       <c r="C449" s="4" t="inlineStr">
         <is>
-          <t>Hamiledyi</t>
+          <t>Sukh</t>
         </is>
       </c>
       <c r="D449" s="4" t="n">
@@ -7997,92 +8039,84 @@
       </c>
     </row>
     <row r="450">
-      <c r="B450" s="7" t="inlineStr">
-        <is>
-          <t>This is my go to sand for my hamsters</t>
-        </is>
-      </c>
-      <c r="C450" s="8" t="inlineStr">
-        <is>
-          <t>BUCATSTATE</t>
-        </is>
-      </c>
-      <c r="D450" s="8" t="n">
+      <c r="A450" s="2" t="inlineStr">
+        <is>
+          <t>Lightweight</t>
+        </is>
+      </c>
+      <c r="B450" s="3" t="inlineStr">
+        <is>
+          <t>pretty lightweight</t>
+        </is>
+      </c>
+      <c r="C450" s="4" t="inlineStr">
+        <is>
+          <t>JFWOD</t>
+        </is>
+      </c>
+      <c r="D450" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E450" s="5">
-        <f>SUM(D450:D450)</f>
+        <f>SUM(D450:D452)</f>
+        <v/>
+      </c>
+      <c r="F450" s="6">
+        <f>SUM(E450:E452)</f>
         <v/>
       </c>
     </row>
     <row r="451">
-      <c r="A451" s="2" t="inlineStr">
-        <is>
-          <t>Cute Flower Petals</t>
-        </is>
-      </c>
       <c r="B451" s="3" t="inlineStr">
         <is>
-          <t>Love the flowers in it</t>
+          <t>not bulky</t>
         </is>
       </c>
       <c r="C451" s="4" t="inlineStr">
         <is>
-          <t>BUCATSTATE</t>
+          <t>JFWOD</t>
         </is>
       </c>
       <c r="D451" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E451" s="5">
-        <f>SUM(D451:D451)</f>
-        <v/>
-      </c>
-      <c r="F451" s="6">
-        <f>SUM(E451:E452)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="452">
-      <c r="B452" s="7" t="inlineStr">
-        <is>
-          <t>The smell of the flowers is also nice</t>
-        </is>
-      </c>
-      <c r="C452" s="8" t="inlineStr">
-        <is>
-          <t>DR_DUDU</t>
-        </is>
-      </c>
-      <c r="D452" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E452" s="5">
-        <f>SUM(D452:D452)</f>
-        <v/>
+      <c r="B452" s="3" t="inlineStr">
+        <is>
+          <t>feels soft and light</t>
+        </is>
+      </c>
+      <c r="C452" s="4" t="inlineStr">
+        <is>
+          <t>JFWOD</t>
+        </is>
+      </c>
+      <c r="D452" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
         <is>
-          <t>Craft / Décor Use</t>
+          <t>Litter Box / Potty Use</t>
         </is>
       </c>
       <c r="B453" s="3" t="inlineStr">
         <is>
-          <t>best sand for crafts</t>
+          <t>My hamster is potty trained</t>
         </is>
       </c>
       <c r="C453" s="4" t="inlineStr">
         <is>
-          <t>DR_DUDU</t>
+          <t>JFWOD</t>
         </is>
       </c>
       <c r="D453" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E453" s="5">
-        <f>SUM(D453:D453)</f>
+        <f>SUM(D453:D454)</f>
         <v/>
       </c>
       <c r="F453" s="6">
@@ -8091,36 +8125,32 @@
       </c>
     </row>
     <row r="454">
-      <c r="B454" s="7" t="inlineStr">
-        <is>
-          <t>best sand for crafts</t>
-        </is>
-      </c>
-      <c r="C454" s="8" t="inlineStr">
-        <is>
-          <t>BUCATSTATE</t>
-        </is>
-      </c>
-      <c r="D454" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E454" s="5">
-        <f>SUM(D454:D454)</f>
-        <v/>
+      <c r="B454" s="3" t="inlineStr">
+        <is>
+          <t>Rollie" relieves herself in the sand much more than in her bedding which is nice so we don't have to change it so often!</t>
+        </is>
+      </c>
+      <c r="C454" s="4" t="inlineStr">
+        <is>
+          <t>JFWOD</t>
+        </is>
+      </c>
+      <c r="D454" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="455">
-      <c r="B455" s="3" t="inlineStr">
-        <is>
-          <t>best sand for crafts</t>
-        </is>
-      </c>
-      <c r="C455" s="4" t="inlineStr">
-        <is>
-          <t>Sukh</t>
-        </is>
-      </c>
-      <c r="D455" s="4" t="n">
+      <c r="B455" s="7" t="inlineStr">
+        <is>
+          <t>My winter white loves to dig, poop, sleep, and eat food in the sand</t>
+        </is>
+      </c>
+      <c r="C455" s="8" t="inlineStr">
+        <is>
+          <t>Hamiledyi</t>
+        </is>
+      </c>
+      <c r="D455" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E455" s="5">
@@ -8131,24 +8161,24 @@
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
         <is>
-          <t>Lightweight</t>
+          <t>Multi-Purpose Use</t>
         </is>
       </c>
       <c r="B456" s="3" t="inlineStr">
         <is>
-          <t>pretty lightweight</t>
+          <t>Works as both a bath sand and a potty litter which makes it versatile for different cage setups depending on how you have things arranged</t>
         </is>
       </c>
       <c r="C456" s="4" t="inlineStr">
         <is>
-          <t>JFWOD</t>
+          <t>Fufuzoie</t>
         </is>
       </c>
       <c r="D456" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E456" s="5">
-        <f>SUM(D456:D458)</f>
+        <f>SUM(D456:D456)</f>
         <v/>
       </c>
       <c r="F456" s="6">
@@ -8157,56 +8187,64 @@
       </c>
     </row>
     <row r="457">
-      <c r="B457" s="3" t="inlineStr">
-        <is>
-          <t>not bulky</t>
-        </is>
-      </c>
-      <c r="C457" s="4" t="inlineStr">
-        <is>
-          <t>JFWOD</t>
-        </is>
-      </c>
-      <c r="D457" s="4" t="n">
-        <v>1</v>
+      <c r="B457" s="7" t="inlineStr">
+        <is>
+          <t>i used it for decorating bases and it works great for that</t>
+        </is>
+      </c>
+      <c r="C457" s="8" t="inlineStr">
+        <is>
+          <t>JFWOD</t>
+        </is>
+      </c>
+      <c r="D457" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E457" s="5">
+        <f>SUM(D457:D457)</f>
+        <v/>
       </c>
     </row>
     <row r="458">
       <c r="B458" s="3" t="inlineStr">
         <is>
-          <t>feels soft and light</t>
+          <t>It worked for my sons project</t>
         </is>
       </c>
       <c r="C458" s="4" t="inlineStr">
         <is>
-          <t>JFWOD</t>
+          <t>Sukh</t>
         </is>
       </c>
       <c r="D458" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="E458" s="5">
+        <f>SUM(D458:D458)</f>
+        <v/>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
         <is>
-          <t>Litter Box / Potty Use</t>
+          <t>Stays Loose, Doesn't Clump</t>
         </is>
       </c>
       <c r="B459" s="3" t="inlineStr">
         <is>
-          <t>My hamster is potty trained</t>
+          <t>stays loose and doesn't clump up</t>
         </is>
       </c>
       <c r="C459" s="4" t="inlineStr">
         <is>
-          <t>JFWOD</t>
+          <t>Fufuzoie</t>
         </is>
       </c>
       <c r="D459" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E459" s="5">
-        <f>SUM(D459:D460)</f>
+        <f>SUM(D459:D461)</f>
         <v/>
       </c>
       <c r="F459" s="6">
@@ -8217,12 +8255,12 @@
     <row r="460">
       <c r="B460" s="3" t="inlineStr">
         <is>
-          <t>Rollie" relieves herself in the sand much more than in her bedding which is nice so we don't have to change it so often!</t>
+          <t>I have not noticed any clumps</t>
         </is>
       </c>
       <c r="C460" s="4" t="inlineStr">
         <is>
-          <t>JFWOD</t>
+          <t>Fufuzoie</t>
         </is>
       </c>
       <c r="D460" s="4" t="n">
@@ -8230,38 +8268,34 @@
       </c>
     </row>
     <row r="461">
-      <c r="B461" s="7" t="inlineStr">
-        <is>
-          <t>My winter white loves to dig, poop, sleep, and eat food in the sand</t>
-        </is>
-      </c>
-      <c r="C461" s="8" t="inlineStr">
-        <is>
-          <t>Hamiledyi</t>
-        </is>
-      </c>
-      <c r="D461" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E461" s="5">
-        <f>SUM(D461:D461)</f>
-        <v/>
+      <c r="B461" s="3" t="inlineStr">
+        <is>
+          <t>The sand stays loose and doesn't clump up on me</t>
+        </is>
+      </c>
+      <c r="C461" s="4" t="inlineStr">
+        <is>
+          <t>Fufuzoie</t>
+        </is>
+      </c>
+      <c r="D461" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
         <is>
-          <t>Multi-Purpose Use</t>
+          <t>Foraging Enrichment</t>
         </is>
       </c>
       <c r="B462" s="3" t="inlineStr">
         <is>
-          <t>Works as both a bath sand and a potty litter which makes it versatile for different cage setups depending on how you have things arranged</t>
+          <t>it also gives the hammies something to forge for</t>
         </is>
       </c>
       <c r="C462" s="4" t="inlineStr">
         <is>
-          <t>Fufuzoie</t>
+          <t>BUCATSTATE</t>
         </is>
       </c>
       <c r="D462" s="4" t="n">
@@ -8272,19 +8306,19 @@
         <v/>
       </c>
       <c r="F462" s="6">
-        <f>SUM(E462:E464)</f>
+        <f>SUM(E462:E463)</f>
         <v/>
       </c>
     </row>
     <row r="463">
       <c r="B463" s="7" t="inlineStr">
         <is>
-          <t>i used it for decorating bases and it works great for that</t>
+          <t>keeping her clean and entertained</t>
         </is>
       </c>
       <c r="C463" s="8" t="inlineStr">
         <is>
-          <t>JFWOD</t>
+          <t>DR_DUDU</t>
         </is>
       </c>
       <c r="D463" s="8" t="n">
@@ -8296,96 +8330,122 @@
       </c>
     </row>
     <row r="464">
+      <c r="A464" s="2" t="inlineStr">
+        <is>
+          <t>Great for Bathing</t>
+        </is>
+      </c>
       <c r="B464" s="3" t="inlineStr">
         <is>
-          <t>It worked for my sons project</t>
+          <t>texture works really well for dust bathing</t>
         </is>
       </c>
       <c r="C464" s="4" t="inlineStr">
         <is>
-          <t>Sukh</t>
+          <t>Fufuzoie</t>
         </is>
       </c>
       <c r="D464" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E464" s="5">
         <f>SUM(D464:D464)</f>
         <v/>
       </c>
+      <c r="F464" s="6">
+        <f>SUM(E464:E464)</f>
+        <v/>
+      </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
         <is>
-          <t>Stays Loose, Doesn't Clump</t>
+          <t>Must Have Product</t>
         </is>
       </c>
       <c r="B465" s="3" t="inlineStr">
         <is>
-          <t>stays loose and doesn't clump up</t>
+          <t>Must have for any hamster cage</t>
         </is>
       </c>
       <c r="C465" s="4" t="inlineStr">
         <is>
+          <t>JFWOD</t>
+        </is>
+      </c>
+      <c r="D465" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E465" s="5">
+        <f>SUM(D465:D465)</f>
+        <v/>
+      </c>
+      <c r="F465" s="6">
+        <f>SUM(E465:E466)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="466">
+      <c r="B466" s="7" t="inlineStr">
+        <is>
+          <t>solid addition to her cage</t>
+        </is>
+      </c>
+      <c r="C466" s="8" t="inlineStr">
+        <is>
           <t>Fufuzoie</t>
         </is>
       </c>
-      <c r="D465" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E465" s="5">
-        <f>SUM(D465:D467)</f>
-        <v/>
-      </c>
-      <c r="F465" s="6">
-        <f>SUM(E465:E467)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="466">
-      <c r="B466" s="3" t="inlineStr">
-        <is>
-          <t>I have not noticed any clumps</t>
-        </is>
-      </c>
-      <c r="C466" s="4" t="inlineStr">
-        <is>
-          <t>Fufuzoie</t>
-        </is>
-      </c>
-      <c r="D466" s="4" t="n">
-        <v>1</v>
+      <c r="D466" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E466" s="5">
+        <f>SUM(D466:D466)</f>
+        <v/>
       </c>
     </row>
     <row r="467">
+      <c r="A467" s="2" t="inlineStr">
+        <is>
+          <t>Keeps Pests Away</t>
+        </is>
+      </c>
       <c r="B467" s="3" t="inlineStr">
         <is>
-          <t>The sand stays loose and doesn't clump up on me</t>
+          <t>it is also proving effective in keeping pests away from my quail</t>
         </is>
       </c>
       <c r="C467" s="4" t="inlineStr">
         <is>
-          <t>Fufuzoie</t>
+          <t>JFWOD</t>
         </is>
       </c>
       <c r="D467" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="E467" s="5">
+        <f>SUM(D467:D467)</f>
+        <v/>
+      </c>
+      <c r="F467" s="6">
+        <f>SUM(E467:E467)</f>
+        <v/>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
         <is>
-          <t>Foraging Enrichment</t>
+          <t>Smells Good</t>
         </is>
       </c>
       <c r="B468" s="3" t="inlineStr">
         <is>
-          <t>it also gives the hammies something to forge for</t>
+          <t>Not peeing in his bedding was great!</t>
         </is>
       </c>
       <c r="C468" s="4" t="inlineStr">
         <is>
-          <t>BUCATSTATE</t>
+          <t>Hamiledyi</t>
         </is>
       </c>
       <c r="D468" s="4" t="n">
@@ -8396,47 +8456,56 @@
         <v/>
       </c>
       <c r="F468" s="6">
-        <f>SUM(E468:E469)</f>
+        <f>SUM(E468:E468)</f>
         <v/>
       </c>
     </row>
     <row r="469">
-      <c r="B469" s="7" t="inlineStr">
-        <is>
-          <t>keeping her clean and entertained</t>
-        </is>
-      </c>
-      <c r="C469" s="8" t="inlineStr">
-        <is>
-          <t>DR_DUDU</t>
-        </is>
-      </c>
-      <c r="D469" s="8" t="n">
+      <c r="A469" s="2" t="inlineStr">
+        <is>
+          <t>Works as Described</t>
+        </is>
+      </c>
+      <c r="B469" s="3" t="inlineStr">
+        <is>
+          <t>this product lives up to its claim</t>
+        </is>
+      </c>
+      <c r="C469" s="4" t="inlineStr">
+        <is>
+          <t>JFWOD</t>
+        </is>
+      </c>
+      <c r="D469" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E469" s="5">
         <f>SUM(D469:D469)</f>
         <v/>
       </c>
+      <c r="F469" s="6">
+        <f>SUM(E469:E469)</f>
+        <v/>
+      </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
         <is>
-          <t>Great for Bathing</t>
+          <t>Works for Multiple Pets</t>
         </is>
       </c>
       <c r="B470" s="3" t="inlineStr">
         <is>
-          <t>texture works really well for dust bathing</t>
+          <t>My foster hamsters and hedgehogs love digging in dr. Dudu</t>
         </is>
       </c>
       <c r="C470" s="4" t="inlineStr">
         <is>
-          <t>Fufuzoie</t>
+          <t>DR_DUDU</t>
         </is>
       </c>
       <c r="D470" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E470" s="5">
         <f>SUM(D470:D470)</f>
@@ -8444,165 +8513,6 @@
       </c>
       <c r="F470" s="6">
         <f>SUM(E470:E470)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="471">
-      <c r="A471" s="2" t="inlineStr">
-        <is>
-          <t>Must Have Product</t>
-        </is>
-      </c>
-      <c r="B471" s="3" t="inlineStr">
-        <is>
-          <t>Must have for any hamster cage</t>
-        </is>
-      </c>
-      <c r="C471" s="4" t="inlineStr">
-        <is>
-          <t>JFWOD</t>
-        </is>
-      </c>
-      <c r="D471" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E471" s="5">
-        <f>SUM(D471:D471)</f>
-        <v/>
-      </c>
-      <c r="F471" s="6">
-        <f>SUM(E471:E472)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="472">
-      <c r="B472" s="7" t="inlineStr">
-        <is>
-          <t>solid addition to her cage</t>
-        </is>
-      </c>
-      <c r="C472" s="8" t="inlineStr">
-        <is>
-          <t>Fufuzoie</t>
-        </is>
-      </c>
-      <c r="D472" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E472" s="5">
-        <f>SUM(D472:D472)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="473">
-      <c r="A473" s="2" t="inlineStr">
-        <is>
-          <t>Keeps Pests Away</t>
-        </is>
-      </c>
-      <c r="B473" s="3" t="inlineStr">
-        <is>
-          <t>it is also proving effective in keeping pests away from my quail</t>
-        </is>
-      </c>
-      <c r="C473" s="4" t="inlineStr">
-        <is>
-          <t>JFWOD</t>
-        </is>
-      </c>
-      <c r="D473" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E473" s="5">
-        <f>SUM(D473:D473)</f>
-        <v/>
-      </c>
-      <c r="F473" s="6">
-        <f>SUM(E473:E473)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="474">
-      <c r="A474" s="2" t="inlineStr">
-        <is>
-          <t>Smells Good</t>
-        </is>
-      </c>
-      <c r="B474" s="3" t="inlineStr">
-        <is>
-          <t>Not peeing in his bedding was great!</t>
-        </is>
-      </c>
-      <c r="C474" s="4" t="inlineStr">
-        <is>
-          <t>Hamiledyi</t>
-        </is>
-      </c>
-      <c r="D474" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E474" s="5">
-        <f>SUM(D474:D474)</f>
-        <v/>
-      </c>
-      <c r="F474" s="6">
-        <f>SUM(E474:E474)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="475">
-      <c r="A475" s="2" t="inlineStr">
-        <is>
-          <t>Works as Described</t>
-        </is>
-      </c>
-      <c r="B475" s="3" t="inlineStr">
-        <is>
-          <t>this product lives up to its claim</t>
-        </is>
-      </c>
-      <c r="C475" s="4" t="inlineStr">
-        <is>
-          <t>JFWOD</t>
-        </is>
-      </c>
-      <c r="D475" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E475" s="5">
-        <f>SUM(D475:D475)</f>
-        <v/>
-      </c>
-      <c r="F475" s="6">
-        <f>SUM(E475:E475)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" s="2" t="inlineStr">
-        <is>
-          <t>Works for Multiple Pets</t>
-        </is>
-      </c>
-      <c r="B476" s="3" t="inlineStr">
-        <is>
-          <t>My foster hamsters and hedgehogs love digging in dr. Dudu</t>
-        </is>
-      </c>
-      <c r="C476" s="4" t="inlineStr">
-        <is>
-          <t>DR_DUDU</t>
-        </is>
-      </c>
-      <c r="D476" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E476" s="5">
-        <f>SUM(D476:D476)</f>
-        <v/>
-      </c>
-      <c r="F476" s="6">
-        <f>SUM(E476:E476)</f>
         <v/>
       </c>
     </row>
